--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.156944781132</v>
+        <v>3669.193162517317</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.453745603976</v>
+        <v>3566.502882950875</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.149297259264</v>
+        <v>3512.206299665061</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.626876958778</v>
+        <v>3484.687651159808</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.155747029851</v>
+        <v>3493.218005761139</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3505.955719130351</v>
+        <v>3506.018712526915</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.465650769396</v>
+        <v>3520.528170381737</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3532.954867130705</v>
+        <v>3533.016383737371</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.73104311828</v>
+        <v>3548.77672182347</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.497313364967</v>
+        <v>3452.485800810078</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.115745098638</v>
+        <v>3450.105609238112</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.208697276041</v>
+        <v>3450.199333010816</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.851588093638</v>
+        <v>3531.801829372716</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.979446573996</v>
+        <v>3627.883684516773</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3778.980291557212</v>
+        <v>3778.834656707865</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3850.377372507849</v>
+        <v>3850.246677640122</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3897.253493366156</v>
+        <v>3897.130325575789</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3882.92168845322</v>
+        <v>3882.814526822695</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.444725914118</v>
+        <v>3886.399351720966</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.469109674255</v>
+        <v>3993.454034232183</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.576832325298</v>
+        <v>4067.532056757997</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.452594515164</v>
+        <v>4107.397382523352</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.327603033869</v>
+        <v>4206.322303571493</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.246185888284</v>
+        <v>4199.224113642794</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.177514344045</v>
+        <v>4223.115756737099</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.972159842546</v>
+        <v>4243.909399027285</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4308.151268804095</v>
+        <v>4308.062833631566</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4400.155515073224</v>
+        <v>4400.043350839658</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4436.037608988754</v>
+        <v>4435.915220345947</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4536.962296051979</v>
+        <v>4536.798181579848</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4671.837435614498</v>
+        <v>4671.638285775452</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4752.580589529776</v>
+        <v>4752.321412036254</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4890.703525202165</v>
+        <v>4890.552901362927</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4931.577421537986</v>
+        <v>4931.411817743601</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5037.159201159449</v>
+        <v>5036.942241483252</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5206.846268370449</v>
+        <v>5206.72157457867</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.948216844551</v>
+        <v>5250.923796352335</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5294.833362150328</v>
+        <v>5294.959299015438</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5373.966648001639</v>
+        <v>5374.207239083667</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5452.158680583507</v>
+        <v>5452.471219486657</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5582.977497488206</v>
+        <v>5583.320565620966</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5524.859889542175</v>
+        <v>5525.301574353317</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5352.228515232719</v>
+        <v>5352.781544615262</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5235.065267950448</v>
+        <v>5235.589163244595</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5102.008110998449</v>
+        <v>5102.576005900056</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4987.025176753367</v>
+        <v>4987.541556327198</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4883.906694249292</v>
+        <v>4884.403781487542</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4836.732780296536</v>
+        <v>4837.295169759852</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4705.985107594932</v>
+        <v>4706.436379854712</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4581.838436427754</v>
+        <v>4582.151477774908</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4483.713767106752</v>
+        <v>4483.918784364477</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4478.958461970486</v>
+        <v>4479.167726396756</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4400.18537939402</v>
+        <v>4400.448220923387</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4244.121870421998</v>
+        <v>4244.476757876513</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4149.240325736473</v>
+        <v>4149.543571999205</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4097.42211919013</v>
+        <v>4097.619530845917</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.822796573654</v>
+        <v>4081.827481769219</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4126.818752657562</v>
+        <v>4126.541832430103</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4206.990032390172</v>
+        <v>4206.3928676132</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4304.365946607568</v>
+        <v>4303.570422168059</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4345.432434106353</v>
+        <v>4347.251205097933</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4349.063903583495</v>
+        <v>4350.702391445611</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4344.031497633135</v>
+        <v>4344.639215867549</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4359.33293397472</v>
+        <v>4358.73489451559</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4407.770535780244</v>
+        <v>4407.132380924369</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4484.491589569188</v>
+        <v>4483.884270508368</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4571.813418340669</v>
+        <v>4571.189423771074</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4699.942019225009</v>
+        <v>4697.172841864474</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4808.343806713377</v>
+        <v>4802.425579679739</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4915.691006714935</v>
+        <v>4907.344594166988</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5042.285460078785</v>
+        <v>5028.050261432132</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5066.109332356533</v>
+        <v>5049.225401274507</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5036.641645260319</v>
+        <v>5018.826706526091</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4795.560792368939</v>
+        <v>4803.372350353277</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.193162517317</v>
+        <v>3669.228617860233</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.502882950875</v>
+        <v>3566.550989565697</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.206299665061</v>
+        <v>3512.262110210288</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.687651159808</v>
+        <v>3484.74715986503</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.218005761139</v>
+        <v>3493.278967880075</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.018712526915</v>
+        <v>3506.080393797232</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.528170381737</v>
+        <v>3520.589387626046</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.016383737371</v>
+        <v>3533.076618866813</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.77672182347</v>
+        <v>3548.821462807612</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.485800810078</v>
+        <v>3452.474535013409</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.105609238112</v>
+        <v>3450.095691215832</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.199333010816</v>
+        <v>3450.190170411282</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.801829372716</v>
+        <v>3531.753131788016</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.883684516773</v>
+        <v>3627.789956431929</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3778.834656707865</v>
+        <v>3778.692095694534</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3850.246677640122</v>
+        <v>3850.11873309532</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3897.130325575789</v>
+        <v>3897.009712472563</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3882.814526822695</v>
+        <v>3882.709569659082</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.399351720966</v>
+        <v>3886.354890059804</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.454034232183</v>
+        <v>3993.439249691313</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.532056757997</v>
+        <v>4067.488205931034</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.397382523352</v>
+        <v>4107.343312706678</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.322303571493</v>
+        <v>4206.317135167655</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.224113642794</v>
+        <v>4199.202538372156</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.115756737099</v>
+        <v>4223.055351632855</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.909399027285</v>
+        <v>4243.847999318428</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4308.062833631566</v>
+        <v>4307.976301306398</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4400.043350839658</v>
+        <v>4399.933580103589</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4435.915220345947</v>
+        <v>4435.795420412929</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4536.798181579848</v>
+        <v>4536.637511423111</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4671.638285775452</v>
+        <v>4671.443322547368</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4752.321412036254</v>
+        <v>4752.067546131391</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4890.552901362927</v>
+        <v>4890.40543266595</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4931.411817743601</v>
+        <v>4931.249680867178</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5036.942241483252</v>
+        <v>5036.729794015468</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5206.72157457867</v>
+        <v>5206.599401664191</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.923796352335</v>
+        <v>5250.899681246264</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5294.959299015438</v>
+        <v>5295.082328627353</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5374.207239083667</v>
+        <v>5374.442586761109</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5452.471219486657</v>
+        <v>5452.776976205841</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5583.320565620966</v>
+        <v>5583.656225863939</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5525.301574353317</v>
+        <v>5525.733894090054</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5352.781544615262</v>
+        <v>5353.322945414786</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5235.589163244595</v>
+        <v>5236.102115969661</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5102.576005900056</v>
+        <v>5103.13215595295</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4987.541556327198</v>
+        <v>4988.047336740512</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4884.403781487542</v>
+        <v>4884.89076869181</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4837.295169759852</v>
+        <v>4837.846140204223</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4706.436379854712</v>
+        <v>4706.878460996335</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4582.151477774908</v>
+        <v>4582.458063439395</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4483.918784364477</v>
+        <v>4484.119432850553</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4479.167726396756</v>
+        <v>4479.372536983275</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4400.448220923387</v>
+        <v>4400.705544761849</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4244.476757876513</v>
+        <v>4244.824373196724</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4149.543571999205</v>
+        <v>4149.84088982028</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4097.619530845917</v>
+        <v>4097.813316140154</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.827481769219</v>
+        <v>4081.832741569387</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4126.541832430103</v>
+        <v>4126.271415095284</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4206.3928676132</v>
+        <v>4205.808568280643</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4303.570422168059</v>
+        <v>4302.791111171231</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4347.251205097933</v>
+        <v>4346.481179425526</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4350.702391445611</v>
+        <v>4351.55854174027</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4344.639215867549</v>
+        <v>4345.827544880898</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4358.73489451559</v>
+        <v>4360.05683150957</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4407.132380924369</v>
+        <v>4409.134288471029</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4483.884270508368</v>
+        <v>4485.096100696457</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4571.189423771074</v>
+        <v>4571.778712295953</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4697.172841864474</v>
+        <v>4692.254772276799</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4802.425579679739</v>
+        <v>4793.655773273253</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4907.344594166988</v>
+        <v>4894.206401359496</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5028.050261432132</v>
+        <v>5007.812028507724</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5049.225401274507</v>
+        <v>5024.135831574427</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>5018.826706526091</v>
+        <v>4988.904466980257</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,15 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4803.372350353277</v>
+        <v>4784.412722433664</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B81">
+        <v>4677.559458529039</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.228617860233</v>
+        <v>3669.263334631169</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.550989565697</v>
+        <v>3566.598097540909</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.262110210288</v>
+        <v>3512.316765883331</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.74715986503</v>
+        <v>3484.80544218365</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.278967880075</v>
+        <v>3493.338673463796</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.080393797232</v>
+        <v>3506.140803504629</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.589387626046</v>
+        <v>3520.649342767494</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.076618866813</v>
+        <v>3533.135612138478</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.821462807612</v>
+        <v>3548.865294629176</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.474535013409</v>
+        <v>3452.463508129218</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.095691215832</v>
+        <v>3450.085984087721</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.190170411282</v>
+        <v>3450.18120303647</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.753131788016</v>
+        <v>3531.705461767105</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.789956431929</v>
+        <v>3627.698198228707</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3778.692095694534</v>
+        <v>3778.552512257409</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3850.11873309532</v>
+        <v>3849.993452987225</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3897.009712472563</v>
+        <v>3896.891575451224</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3882.709569659082</v>
+        <v>3882.606749707299</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.354890059804</v>
+        <v>3886.311313741374</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.439249691313</v>
+        <v>3993.424747774545</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.488205931034</v>
+        <v>4067.445251494388</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.343312706678</v>
+        <v>4107.290349997495</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.317135167655</v>
+        <v>4206.312093125036</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.202538372156</v>
+        <v>4199.181443563617</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4223.055351632855</v>
+        <v>4222.99625519439</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.847999318428</v>
+        <v>4243.787917025307</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.976301306398</v>
+        <v>4307.891611209494</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4399.933580103589</v>
+        <v>4399.826127231973</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4435.795420412929</v>
+        <v>4435.6781280536</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4536.637511423111</v>
+        <v>4536.48017842035</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4671.443322547368</v>
+        <v>4671.252415481677</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4752.067546131391</v>
+        <v>4751.818830425063</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4890.40543266595</v>
+        <v>4890.261021163383</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4931.249680867178</v>
+        <v>4931.090903342274</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5036.729794015468</v>
+        <v>5036.521719751876</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5206.599401664191</v>
+        <v>5206.479674192066</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.899681246264</v>
+        <v>5250.875868500152</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5295.082328627353</v>
+        <v>5295.202549636055</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5374.442586761109</v>
+        <v>5374.672860173786</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5452.776976205841</v>
+        <v>5453.076168559807</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5583.656225863939</v>
+        <v>5583.98471508589</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5525.733894090054</v>
+        <v>5526.157143044862</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5353.322945414786</v>
+        <v>5353.853079874142</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5236.102115969661</v>
+        <v>5236.604464696698</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5103.13215595295</v>
+        <v>5103.676920915752</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4988.047336740512</v>
+        <v>4988.542840344564</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4884.89076869181</v>
+        <v>4885.367959813296</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4837.846140204223</v>
+        <v>4838.386034972396</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4706.878460996335</v>
+        <v>4707.311628327467</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4582.458063439395</v>
+        <v>4582.758390732617</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4484.119432850553</v>
+        <v>4484.315850419831</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4479.372536983275</v>
+        <v>4479.57303415227</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4400.705544761849</v>
+        <v>4400.957522457487</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4244.824373196724</v>
+        <v>4245.164936704989</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4149.84088982028</v>
+        <v>4150.132449671683</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4097.813316140154</v>
+        <v>4098.003571870311</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.832741569387</v>
+        <v>4081.838538423244</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4126.271415095284</v>
+        <v>4126.007280756152</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4205.808568280643</v>
+        <v>4205.236731281791</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4302.791111171231</v>
+        <v>4302.027534718831</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4346.481179425526</v>
+        <v>4345.725317148232</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4351.55854174027</v>
+        <v>4352.387756687958</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4345.827544880898</v>
+        <v>4346.998623730216</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4360.05683150957</v>
+        <v>4361.328405887327</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4409.134288471029</v>
+        <v>4411.069580779648</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4485.096100696457</v>
+        <v>4486.275942365639</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4571.778712295953</v>
+        <v>4572.364350095879</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4692.254772276799</v>
+        <v>4687.621903770567</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4793.655773273253</v>
+        <v>4785.431656035129</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4894.206401359496</v>
+        <v>4881.951532260147</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>5007.812028507724</v>
+        <v>4989.171496069804</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5024.135831574427</v>
+        <v>5001.519106900858</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4988.904466980257</v>
+        <v>4963.017209616502</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4784.412722433664</v>
+        <v>4769.614878059941</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4677.559458529039</v>
+        <v>4677.158960926285</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.263334631169</v>
+        <v>3669.297335669265</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.598097540909</v>
+        <v>3566.644237650477</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.316765883331</v>
+        <v>3512.370302157934</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.80544218365</v>
+        <v>3484.862535630212</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.338673463796</v>
+        <v>3493.39716095505</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.140803504629</v>
+        <v>3506.199980557946</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.649342767494</v>
+        <v>3520.708074428781</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.135612138478</v>
+        <v>3533.193401555672</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.865294629176</v>
+        <v>3548.908244699575</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.463508129218</v>
+        <v>3452.452712640741</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.085984087721</v>
+        <v>3450.076481201597</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.18120303647</v>
+        <v>3450.172424716659</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.705461767105</v>
+        <v>3531.658787138452</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.698198228707</v>
+        <v>3627.608348479828</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3778.552512257409</v>
+        <v>3778.415814112795</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3849.993452987225</v>
+        <v>3849.870754967765</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3896.891575451224</v>
+        <v>3896.775839096095</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3882.606749707299</v>
+        <v>3882.506002417423</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.311313741374</v>
+        <v>3886.268596643234</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.424747774545</v>
+        <v>3993.410520513128</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.445251494388</v>
+        <v>4067.40316624498</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.290349997495</v>
+        <v>4107.238460748687</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.312093125036</v>
+        <v>4206.307172964511</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.181443563617</v>
+        <v>4199.160813424729</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.99625519439</v>
+        <v>4222.938425454604</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.787917025307</v>
+        <v>4243.72911030297</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.891611209494</v>
+        <v>4307.808705263935</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4399.826127231973</v>
+        <v>4399.720919738336</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4435.6781280536</v>
+        <v>4435.563265481967</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4536.48017842035</v>
+        <v>4536.326079804187</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4671.252415481677</v>
+        <v>4671.065439485617</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4751.818830425063</v>
+        <v>4751.57510999026</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4890.261021163383</v>
+        <v>4890.11957291356</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4931.090903342274</v>
+        <v>4930.935381999672</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5036.521719751876</v>
+        <v>5036.317885327202</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5206.479674192066</v>
+        <v>5206.362319697134</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.875868500152</v>
+        <v>5250.852354944673</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5295.202549636055</v>
+        <v>5295.32005631062</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5374.672860173786</v>
+        <v>5374.89822128085</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5453.076168559807</v>
+        <v>5453.369005161387</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5583.98471508589</v>
+        <v>5584.306260183601</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5526.157143044862</v>
+        <v>5526.571603324911</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5353.853079874142</v>
+        <v>5354.372295373938</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5236.604464696698</v>
+        <v>5237.096534201015</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5103.676920915752</v>
+        <v>5104.210646037514</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4988.542840344564</v>
+        <v>4989.028376577584</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4885.367959813296</v>
+        <v>4885.835646760088</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4838.386034972396</v>
+        <v>4838.915183817893</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4707.311628327467</v>
+        <v>4707.736148138022</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4582.758390732617</v>
+        <v>4583.052649020384</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4484.315850419831</v>
+        <v>4484.508169200184</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4479.57303415227</v>
+        <v>4479.769352495066</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4400.957522457487</v>
+        <v>4401.204318535798</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4245.164936704989</v>
+        <v>4245.498659950744</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4150.132449671683</v>
+        <v>4150.418415622915</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4098.003571870311</v>
+        <v>4098.190391516573</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.838538423244</v>
+        <v>4081.844837070155</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4126.007280756152</v>
+        <v>4125.749219090832</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4205.236731281791</v>
+        <v>4204.676969857084</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4302.027534718831</v>
+        <v>4301.279232116134</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4345.725317148232</v>
+        <v>4344.983248261067</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4352.387756687958</v>
+        <v>4352.244412188451</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4346.998623730216</v>
+        <v>4346.992808831685</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4361.328405887327</v>
+        <v>4361.488643812723</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4411.069580779648</v>
+        <v>4411.623101977346</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4486.275942365639</v>
+        <v>4485.948787785985</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4572.364350095879</v>
+        <v>4569.216588304691</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4687.621903770567</v>
+        <v>4681.532301408644</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4785.431656035129</v>
+        <v>4775.695813352362</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4881.951532260147</v>
+        <v>4868.179461771045</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4989.171496069804</v>
+        <v>4969.115950437696</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>5001.519106900858</v>
+        <v>4977.410277088762</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4963.017209616502</v>
+        <v>4935.434201523207</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4769.614878059941</v>
+        <v>4749.82093387004</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4677.158960926285</v>
+        <v>4650.795852108832</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.297335669265</v>
+        <v>3669.330642881624</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.644237650477</v>
+        <v>3566.689439416894</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.370302157934</v>
+        <v>3512.422753069942</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.862535630212</v>
+        <v>3484.918476205027</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.39716095505</v>
+        <v>3493.454467244654</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.199980557946</v>
+        <v>3506.257962295012</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.708074428781</v>
+        <v>3520.765619673008</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.193401555672</v>
+        <v>3533.250023587106</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.908244699575</v>
+        <v>3548.950339340135</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.452712640741</v>
+        <v>3452.442141343133</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.076481201597</v>
+        <v>3450.067176181988</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.172424716659</v>
+        <v>3450.163829539232</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.658787138452</v>
+        <v>3531.613077059145</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.608348479828</v>
+        <v>3627.520348284611</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3778.415814112795</v>
+        <v>3778.28191275</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3849.870754967765</v>
+        <v>3849.750560046733</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3896.775839096095</v>
+        <v>3896.662431021051</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3882.506002417423</v>
+        <v>3882.407265810182</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.268596643234</v>
+        <v>3886.226713658079</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.410520513128</v>
+        <v>3993.396560232582</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.40316624498</v>
+        <v>4067.361924069256</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.238460748687</v>
+        <v>4107.187612662488</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.307172964511</v>
+        <v>4206.302370412777</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.160813424729</v>
+        <v>4199.140632844649</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.938425454604</v>
+        <v>4222.88182221778</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.72911030297</v>
+        <v>4243.671539055952</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.808705263935</v>
+        <v>4307.727527803378</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4399.720919738336</v>
+        <v>4399.617888121169</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4435.563265481967</v>
+        <v>4435.450758091287</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4536.326079804187</v>
+        <v>4536.175116978651</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4671.065439485617</v>
+        <v>4670.882274550551</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4751.57510999026</v>
+        <v>4751.336236043246</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4890.11957291356</v>
+        <v>4889.980997778583</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4930.935381999672</v>
+        <v>4930.783017845313</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5036.317885327202</v>
+        <v>5036.118162732667</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5206.362319697134</v>
+        <v>5206.247268539826</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.852354944673</v>
+        <v>5250.829137288263</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5295.32005631062</v>
+        <v>5295.434938778224</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5374.89822128085</v>
+        <v>5375.118825237018</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5453.369005161387</v>
+        <v>5453.655685897663</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5584.306260183601</v>
+        <v>5584.621078600177</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5526.571603324911</v>
+        <v>5526.977545475382</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5354.372295373938</v>
+        <v>5354.880925185565</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5237.096534201015</v>
+        <v>5237.578636156296</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5104.210646037514</v>
+        <v>5104.733662780154</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4989.028376577584</v>
+        <v>4989.504242603593</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4885.835646760088</v>
+        <v>4886.294109986156</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4838.915183817893</v>
+        <v>4839.43390356875</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4707.736148138022</v>
+        <v>4708.152276240614</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4583.052649020384</v>
+        <v>4583.34102011818</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4484.508169200184</v>
+        <v>4484.696515886231</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4479.769352495066</v>
+        <v>4479.961621071098</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4401.204318535798</v>
+        <v>4401.446090854595</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4245.498659950744</v>
+        <v>4245.825746140927</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4150.418415622915</v>
+        <v>4150.698945635027</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4098.190391516573</v>
+        <v>4098.373865377323</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.844837070155</v>
+        <v>4081.851604388725</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4125.749219090832</v>
+        <v>4125.497028847261</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4204.676969857084</v>
+        <v>4204.128912792668</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4301.279232116134</v>
+        <v>4300.545760039219</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4344.983248261067</v>
+        <v>4344.254614793977</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4352.244412188451</v>
+        <v>4351.081706089341</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4346.992808831685</v>
+        <v>4345.743864730242</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4361.488643812723</v>
+        <v>4360.428798440523</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4411.623101977346</v>
+        <v>4410.665804282753</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4485.948787785985</v>
+        <v>4484.048902588795</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4569.216588304691</v>
+        <v>4564.527853707261</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4681.532301408644</v>
+        <v>4673.82146231947</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4775.695813352362</v>
+        <v>4764.247805747707</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4868.179461771045</v>
+        <v>4852.645575712186</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4969.115950437696</v>
+        <v>4947.323180756213</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4977.410277088762</v>
+        <v>4951.398760119553</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4935.434201523207</v>
+        <v>4905.620227096013</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4749.82093387004</v>
+        <v>4725.068220767785</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4650.795852108832</v>
+        <v>4614.172570983246</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.330642881624</v>
+        <v>3669.363277290363</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.689439416894</v>
+        <v>3566.733731174145</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.422753069942</v>
+        <v>3512.474151289406</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.918476205027</v>
+        <v>3484.973298469801</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.454467244654</v>
+        <v>3493.510627748998</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.257962295012</v>
+        <v>3506.314784561127</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.765619673008</v>
+        <v>3520.8220140816</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.250023587106</v>
+        <v>3533.30551324357</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.950339340135</v>
+        <v>3548.9916038357</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.442141343133</v>
+        <v>3452.431787327468</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.067176181988</v>
+        <v>3450.058062915906</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.163829539232</v>
+        <v>3450.155411835443</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.613077059145</v>
+        <v>3531.568301947028</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.520348284611</v>
+        <v>3627.434141140453</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3778.28191275</v>
+        <v>3778.150723240538</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3849.750560046733</v>
+        <v>3849.632792422414</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3896.662431021051</v>
+        <v>3896.551281719017</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3882.407265810182</v>
+        <v>3882.310480350403</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.226713658079</v>
+        <v>3886.185640645038</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.396560232582</v>
+        <v>3993.382859539371</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.361924069256</v>
+        <v>4067.321499889197</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.187612662488</v>
+        <v>4107.137774723536</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.302370412777</v>
+        <v>4206.297681390814</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.140632844649</v>
+        <v>4199.120887357896</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.88182221778</v>
+        <v>4222.826406967299</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.671539055952</v>
+        <v>4243.615164847984</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.727527803378</v>
+        <v>4307.648025448521</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4399.617888121169</v>
+        <v>4399.516965712139</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4435.450758091287</v>
+        <v>4435.340534293523</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4536.175116978651</v>
+        <v>4536.027195309909</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4670.882274550551</v>
+        <v>4670.702805496632</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4751.336236043246</v>
+        <v>4751.102065642509</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4889.980997778583</v>
+        <v>4889.845209234021</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4930.783017845313</v>
+        <v>4930.633715851536</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5036.118162732667</v>
+        <v>5035.922429050336</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5206.247268539826</v>
+        <v>5206.134453770262</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.829137288263</v>
+        <v>5250.80621213594</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5295.434938778224</v>
+        <v>5295.547283247766</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5375.118825237018</v>
+        <v>5375.334820745475</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5453.655685897663</v>
+        <v>5453.936402380437</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5584.621078600177</v>
+        <v>5584.929378811436</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5526.977545475382</v>
+        <v>5527.375229064999</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5354.880925185565</v>
+        <v>5355.379289179001</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5237.578636156296</v>
+        <v>5238.051069787312</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5104.733662780154</v>
+        <v>5105.246289498225</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4989.504242603593</v>
+        <v>4989.970723913733</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4886.294109986156</v>
+        <v>4886.743619046205</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4839.43390356875</v>
+        <v>4839.942498752873</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4708.152276240614</v>
+        <v>4708.560258479573</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4583.34102011818</v>
+        <v>4583.623678663091</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4484.696515886231</v>
+        <v>4484.881012015204</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4479.961621071098</v>
+        <v>4480.149963688749</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4401.446090854595</v>
+        <v>4401.682990937671</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4245.825746140927</v>
+        <v>4246.146390545416</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4150.698945635027</v>
+        <v>4150.974191838843</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4098.373865377323</v>
+        <v>4098.554080698431</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.851604388725</v>
+        <v>4081.858809256742</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4125.497028847261</v>
+        <v>4125.250517369024</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4204.128912792668</v>
+        <v>4203.592203661179</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4300.545760039219</v>
+        <v>4299.826691746049</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4344.254614793977</v>
+        <v>4343.539070367809</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4351.081706089341</v>
+        <v>4349.99075755945</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4345.743864730242</v>
+        <v>4344.544353110983</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4360.428798440523</v>
+        <v>4359.343513094211</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4410.665804282753</v>
+        <v>4409.059942897638</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4484.048902588795</v>
+        <v>4481.705182408147</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4564.527853707261</v>
+        <v>4561.390971373805</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4673.82146231947</v>
+        <v>4665.934463315658</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4764.247805747707</v>
+        <v>4752.728471712572</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4852.645575712186</v>
+        <v>4837.217283567437</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4947.323180756213</v>
+        <v>4926.071657711853</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4951.398760119553</v>
+        <v>4926.418575007589</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4905.620227096013</v>
+        <v>4877.606887724287</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4725.068220767785</v>
+        <v>4702.095967392851</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4614.172570983246</v>
+        <v>4586.278478002161</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.363277290363</v>
+        <v>3669.395259076858</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.733731174145</v>
+        <v>3566.777140126915</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.474151289406</v>
+        <v>3512.524528188407</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3484.973298469801</v>
+        <v>3485.027035618752</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.510627748998</v>
+        <v>3493.565676482961</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.314784561127</v>
+        <v>3506.370481782873</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.8220140816</v>
+        <v>3520.877291827591</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.30551324357</v>
+        <v>3533.359904150045</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3548.9916038357</v>
+        <v>3549.032062485121</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.431787327468</v>
+        <v>3452.421643965698</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.058062915906</v>
+        <v>3450.049135539485</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.155411835443</v>
+        <v>3450.147166167974</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.568301947028</v>
+        <v>3531.524433416954</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.434141140453</v>
+        <v>3627.349672822055</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3778.150723240538</v>
+        <v>3778.022164058789</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3849.632792422414</v>
+        <v>3849.517379322348</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3896.551281719017</v>
+        <v>3896.442324420347</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3882.310480350403</v>
+        <v>3882.215588827839</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.185640645038</v>
+        <v>3886.145354383731</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.382859539371</v>
+        <v>3993.369411308288</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.321499889197</v>
+        <v>4067.281869611495</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.137774723536</v>
+        <v>4107.088917135864</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.297681390814</v>
+        <v>4206.293102003108</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.120887357896</v>
+        <v>4199.1015631104</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.826406967299</v>
+        <v>4222.772142779047</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.615164847984</v>
+        <v>4243.559950817241</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.648025448521</v>
+        <v>4307.570146991085</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4399.516965712139</v>
+        <v>4399.418088533479</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4435.340534293523</v>
+        <v>4435.23252536843</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4536.027195309909</v>
+        <v>4535.882223929464</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4670.702805496632</v>
+        <v>4670.526921732699</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4751.102065642509</v>
+        <v>4750.872461405206</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4889.845209234021</v>
+        <v>4889.712124189928</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4930.633715851536</v>
+        <v>4930.487384760701</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5035.922429050336</v>
+        <v>5035.730566203062</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5206.134453770262</v>
+        <v>5206.023811000091</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.80621213594</v>
+        <v>5250.783576006238</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5295.547283247766</v>
+        <v>5295.657172219229</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5375.334820745475</v>
+        <v>5375.546350389035</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5453.936402380437</v>
+        <v>5454.211338369146</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5584.929378811436</v>
+        <v>5585.231360782602</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5527.375229064999</v>
+        <v>5527.764903236359</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5355.379289179001</v>
+        <v>5355.867694488506</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5238.051069787312</v>
+        <v>5238.514122484085</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5105.246289498225</v>
+        <v>5105.748832078994</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4989.970723913733</v>
+        <v>4990.42809489269</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4886.743619046205</v>
+        <v>4887.184433118671</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4839.942498752873</v>
+        <v>4840.441262187522</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4708.560258479573</v>
+        <v>4708.960331210664</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4583.623678663091</v>
+        <v>4583.900792464013</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4484.881012015204</v>
+        <v>4485.061774226196</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4480.149963688749</v>
+        <v>4480.334499169263</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4401.682990937671</v>
+        <v>4401.915164288663</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4246.146390545416</v>
+        <v>4246.460780879155</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4150.974191838843</v>
+        <v>4151.244300798309</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4098.554080698431</v>
+        <v>4098.731121796589</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.858809256742</v>
+        <v>4081.866422421244</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4125.250517369024</v>
+        <v>4125.009500150098</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4203.592203661179</v>
+        <v>4203.066500105784</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4299.826691746049</v>
+        <v>4299.121616328807</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4343.539070367809</v>
+        <v>4342.836279766889</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4349.99075755945</v>
+        <v>4349.299038529043</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4344.544353110983</v>
+        <v>4343.839080465171</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4359.343513094211</v>
+        <v>4358.732944599682</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4409.059942897638</v>
+        <v>4408.012705707373</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4481.705182408147</v>
+        <v>4479.953197190329</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4561.390971373805</v>
+        <v>4558.889347349959</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4665.934463315658</v>
+        <v>4659.11487481569</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4752.728471712572</v>
+        <v>4742.620394894906</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4837.217283567437</v>
+        <v>4823.590162693981</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4926.071657711853</v>
+        <v>4907.335023818232</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4926.418575007589</v>
+        <v>4904.81199371509</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4877.606887724287</v>
+        <v>4854.278935721337</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4702.095967392851</v>
+        <v>4685.078342307932</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4586.278478002161</v>
+        <v>4572.734820403131</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.395259076858</v>
+        <v>3669.426607623354</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.777140126915</v>
+        <v>3566.819692406295</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.524528188407</v>
+        <v>3512.573913904867</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.027035618752</v>
+        <v>3485.079719545578</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.565676482961</v>
+        <v>3493.619646128547</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.370481782873</v>
+        <v>3506.425087037615</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.877291827591</v>
+        <v>3520.931485744612</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.359904150045</v>
+        <v>3533.413228613578</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.032062485121</v>
+        <v>3549.071738648804</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.421643965698</v>
+        <v>3452.411704896537</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.049135539485</v>
+        <v>3450.04038842542</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.147166167974</v>
+        <v>3450.139087319251</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.524433416954</v>
+        <v>3531.48144422087</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.349672822055</v>
+        <v>3627.266891267896</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3778.022164058789</v>
+        <v>3777.896156913321</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3849.517379322348</v>
+        <v>3849.40425085355</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3896.442324420347</v>
+        <v>3896.335494959475</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3882.215588827839</v>
+        <v>3882.122536244902</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.145354383731</v>
+        <v>3886.105832530929</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.369411308288</v>
+        <v>3993.356208670511</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.281869611495</v>
+        <v>4067.243010079697</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.088917135864</v>
+        <v>4107.041011263582</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.293102003108</v>
+        <v>4206.288628527571</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.1015631104</v>
+        <v>4199.082646827652</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.772142779047</v>
+        <v>4222.718994240124</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.559950817241</v>
+        <v>4243.505861596697</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.570146991085</v>
+        <v>4307.493843284765</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4399.418088533479</v>
+        <v>4399.321195163875</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4435.23252536843</v>
+        <v>4435.126665321588</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4535.882223929464</v>
+        <v>4535.740115548954</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4670.526921732699</v>
+        <v>4670.354517030317</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4750.872461405206</v>
+        <v>4750.647291239939</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4889.712124189928</v>
+        <v>4889.581662822347</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4930.487384760701</v>
+        <v>4930.343936900337</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5035.730566203062</v>
+        <v>5035.542460719014</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5206.023811000091</v>
+        <v>5205.915278281554</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.783576006238</v>
+        <v>5250.761225346439</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5295.657172219229</v>
+        <v>5295.764684679825</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5375.546350389035</v>
+        <v>5375.753550941194</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5454.211338369146</v>
+        <v>5454.480670168155</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5585.231360782602</v>
+        <v>5585.52721639743</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5527.764903236359</v>
+        <v>5528.146807223535</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5355.867694488506</v>
+        <v>5356.346436139085</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5238.514122484085</v>
+        <v>5238.968070380106</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5105.748832078994</v>
+        <v>5106.241584545427</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4990.42809489269</v>
+        <v>4990.876619352492</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4887.184433118671</v>
+        <v>4887.616801498981</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4840.441262187522</v>
+        <v>4840.930475535332</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4708.960331210664</v>
+        <v>4709.352721753421</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4583.900792464013</v>
+        <v>4584.172522831588</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4485.061774226196</v>
+        <v>4485.238914503975</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4480.334499169263</v>
+        <v>4480.515341594933</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4401.915164288663</v>
+        <v>4402.142750686476</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4246.460780879155</v>
+        <v>4246.769097662517</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4151.244300798309</v>
+        <v>4151.509413759911</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4098.731121796589</v>
+        <v>4098.905070177043</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.866422421244</v>
+        <v>4081.874416377875</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4125.009500150098</v>
+        <v>4124.773800416529</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4203.066500105784</v>
+        <v>4202.551473164676</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4299.121616328807</v>
+        <v>4298.430138005095</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4342.836279766889</v>
+        <v>4342.145918527754</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4349.299038529043</v>
+        <v>4348.71036927796</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4343.839080465171</v>
+        <v>4341.525058363725</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4358.732944599682</v>
+        <v>4355.509198039063</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4408.012705707373</v>
+        <v>4404.475743505551</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4479.953197190329</v>
+        <v>4474.525922812565</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4558.889347349959</v>
+        <v>4551.361711378098</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4659.11487481569</v>
+        <v>4647.870747450448</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4742.620394894906</v>
+        <v>4726.762829910788</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4823.590162693981</v>
+        <v>4802.892124186957</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4907.335023818232</v>
+        <v>4879.727908046683</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4904.81199371509</v>
+        <v>4871.611793213379</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4854.278935721337</v>
+        <v>4814.943735578281</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4685.078342307932</v>
+        <v>4642.921518655928</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,15 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4572.734820403131</v>
+        <v>4506.727994053665</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B82">
+        <v>4306.271744053664</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.426607623354</v>
+        <v>3669.457341552136</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.819692406295</v>
+        <v>3566.861413122218</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.573913904867</v>
+        <v>3512.622337402646</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.079719545578</v>
+        <v>3485.131380906508</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.619646128547</v>
+        <v>3493.672568099515</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.425087037615</v>
+        <v>3506.478632118923</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.931485744612</v>
+        <v>3520.984627391859</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.413228613578</v>
+        <v>3533.465517687221</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.071738648804</v>
+        <v>3549.110654793554</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.411704896537</v>
+        <v>3452.401964012171</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.04038842542</v>
+        <v>3450.031816171164</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.139087319251</v>
+        <v>3450.131170280462</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.48144422087</v>
+        <v>3531.439308191463</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.266891267896</v>
+        <v>3627.185746473405</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3777.896156913321</v>
+        <v>3777.772626588152</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3849.40425085355</v>
+        <v>3849.293339861519</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3896.335494959475</v>
+        <v>3896.230731649281</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3882.122536244902</v>
+        <v>3882.031269710836</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.105832530929</v>
+        <v>3886.067053579614</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.356208670511</v>
+        <v>3993.343245002267</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.243010079697</v>
+        <v>4067.204899029115</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4107.041011263582</v>
+        <v>4106.994029574976</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.288628527571</v>
+        <v>4206.284257406112</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.082646827652</v>
+        <v>4199.064125784819</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.718994240124</v>
+        <v>4222.666927372464</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.505861596697</v>
+        <v>4243.452863239283</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.493843284765</v>
+        <v>4307.419067142675</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4399.321195163875</v>
+        <v>4399.226226612284</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4435.126665321588</v>
+        <v>4435.022890750777</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4535.740115548954</v>
+        <v>4535.600786285762</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4670.354517030317</v>
+        <v>4670.185489311038</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4750.647291239939</v>
+        <v>4750.426428094781</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4889.581662822347</v>
+        <v>4889.453748414651</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4930.343936900337</v>
+        <v>4930.203288009058</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5035.542460719014</v>
+        <v>5035.358003509777</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5205.915278281554</v>
+        <v>5205.808795993327</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.761225346439</v>
+        <v>5250.739156546282</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5295.764684679825</v>
+        <v>5295.8698962879</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5375.753550941194</v>
+        <v>5375.956553658412</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5454.480670168155</v>
+        <v>5454.744567000226</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5585.52721639743</v>
+        <v>5585.817129861676</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5528.146807223535</v>
+        <v>5528.521170839173</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5356.346436139085</v>
+        <v>5356.815797636411</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5238.968070380106</v>
+        <v>5239.413178897061</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5106.241584545427</v>
+        <v>5106.724829624613</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4990.876619352492</v>
+        <v>4991.316551035896</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4887.616801498981</v>
+        <v>4888.040964065003</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4840.930475535332</v>
+        <v>4841.410409829035</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4709.352721753421</v>
+        <v>4709.737648817917</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4584.172522831588</v>
+        <v>4584.439024889219</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4485.238914503975</v>
+        <v>4485.412540408386</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4480.515341594933</v>
+        <v>4480.69260054265</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4402.142750686476</v>
+        <v>4402.365884463503</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4246.769097662517</v>
+        <v>4247.071514561317</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4151.509413759911</v>
+        <v>4151.769666888963</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4098.905070177043</v>
+        <v>4099.076004645949</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.874416377875</v>
+        <v>4081.882765258832</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4124.773800416529</v>
+        <v>4124.543248733178</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4202.551473164676</v>
+        <v>4202.046806633442</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4298.430138005095</v>
+        <v>4297.751875445722</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4342.145918527754</v>
+        <v>4341.467672543564</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4348.71036927796</v>
+        <v>4348.131069892881</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4341.525058363725</v>
+        <v>4340.95204932406</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4355.509198039063</v>
+        <v>4354.419999091218</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4404.475743505551</v>
+        <v>4403.091308521076</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4474.525922812565</v>
+        <v>4471.697766142136</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4551.361711378098</v>
+        <v>4546.71493840554</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4647.870747450448</v>
+        <v>4640.017522231286</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4726.762829910788</v>
+        <v>4714.987175357841</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4802.892124186957</v>
+        <v>4787.030728578972</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4879.727908046683</v>
+        <v>4858.272489011018</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4871.611793213379</v>
+        <v>4846.30171463638</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4814.943735578281</v>
+        <v>4786.215617615252</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4642.921518655928</v>
+        <v>4615.725556339088</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4506.727994053665</v>
+        <v>4474.150938950611</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4306.271744053664</v>
+        <v>4273.694688950611</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4340.95204932406</v>
+        <v>4341.164298111489</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4354.419999091218</v>
+        <v>4354.68707125831</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4403.091308521076</v>
+        <v>4403.388842494099</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4471.697766142136</v>
+        <v>4472.097986848677</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4546.71493840554</v>
+        <v>4547.188783367129</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4640.017522231286</v>
+        <v>4640.581756932947</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4714.987175357841</v>
+        <v>4715.653865500273</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4787.030728578972</v>
+        <v>4787.808855470877</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4858.272489011018</v>
+        <v>4859.23250232907</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4846.30171463638</v>
+        <v>4847.516025310391</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4786.215617615252</v>
+        <v>4787.802270482006</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4615.725556339088</v>
+        <v>4617.943631486554</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4474.150938950611</v>
+        <v>4478.261616451669</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4273.694688950611</v>
+        <v>4277.805366451669</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.457341552136</v>
+        <v>3669.487478762408</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.861413122218</v>
+        <v>3566.902326412856</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.622337402646</v>
+        <v>3512.669826528147</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.131380906508</v>
+        <v>3485.182049179727</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.672568099515</v>
+        <v>3493.724472602294</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.478632118923</v>
+        <v>3506.531147598255</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3520.984627391859</v>
+        <v>3521.036747115319</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.465517687221</v>
+        <v>3533.516801230265</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.110654793554</v>
+        <v>3549.148832534864</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.401964012171</v>
+        <v>3452.39241544577</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.031816171164</v>
+        <v>3450.023413587825</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.131170280462</v>
+        <v>3450.123410241222</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.439308191463</v>
+        <v>3531.398000189119</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.185746473405</v>
+        <v>3627.106190390408</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3777.772626588152</v>
+        <v>3777.65150079325</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3849.293339861519</v>
+        <v>3849.184581797456</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3896.230731649281</v>
+        <v>3896.127975162652</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3882.031269710836</v>
+        <v>3881.941738341883</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.067053579614</v>
+        <v>3886.028996820322</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.343245002267</v>
+        <v>3993.330513914111</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.204899029115</v>
+        <v>4067.167515044316</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.994029574976</v>
+        <v>4106.94794558981</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.284257406112</v>
+        <v>4206.279985235819</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.064125784819</v>
+        <v>4199.045987778699</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.666927372464</v>
+        <v>4222.61590956104</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.452863239283</v>
+        <v>4243.400923147472</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.419067142675</v>
+        <v>4307.345773240851</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4399.226226612284</v>
+        <v>4399.133126199129</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4435.022890750777</v>
+        <v>4434.921140720118</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4535.600786285762</v>
+        <v>4535.464155498706</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4670.185489311038</v>
+        <v>4670.019740445962</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4750.426428094781</v>
+        <v>4750.209749719545</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4889.453748414651</v>
+        <v>4889.328307208012</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4930.203288009058</v>
+        <v>4930.065357072504</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5035.358003509777</v>
+        <v>5035.177089661131</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5205.808795993327</v>
+        <v>5205.704306732665</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.739156546282</v>
+        <v>5250.717365950262</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5295.8698962879</v>
+        <v>5295.972879545438</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5375.956553658412</v>
+        <v>5376.155484554974</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5454.744567000226</v>
+        <v>5455.00319135779</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5585.817129861676</v>
+        <v>5586.101278082657</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5528.521170839173</v>
+        <v>5528.888214933178</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5356.815797636411</v>
+        <v>5357.276051522653</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5239.413178897061</v>
+        <v>5239.849703258281</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5106.724829624613</v>
+        <v>5107.198839283901</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4991.316551035896</v>
+        <v>4991.748134091339</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4888.040964065003</v>
+        <v>4888.457151716513</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4841.410409829035</v>
+        <v>4841.88132596692</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4709.737648817917</v>
+        <v>4710.11532290763</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4584.439024889219</v>
+        <v>4584.700447866428</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4485.412540408386</v>
+        <v>4485.58275529036</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4480.69260054265</v>
+        <v>4480.866381303775</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4402.365884463503</v>
+        <v>4402.584694767826</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4247.071514561317</v>
+        <v>4247.36819870781</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4151.769666888963</v>
+        <v>4152.025191493582</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4099.076004645949</v>
+        <v>4099.244001417636</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.882765258832</v>
+        <v>4081.891444728711</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4124.543248733178</v>
+        <v>4124.317682633819</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4202.046806633442</v>
+        <v>4201.552196462859</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4297.751875445722</v>
+        <v>4297.086461137024</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4341.467672543564</v>
+        <v>4340.80123768368</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4348.131069892881</v>
+        <v>4347.560935874893</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4341.164298111489</v>
+        <v>4341.459722644114</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4354.68707125831</v>
+        <v>4354.666429465867</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4403.388842494099</v>
+        <v>4403.144517715618</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4472.097986848677</v>
+        <v>4470.718926693156</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4547.188783367129</v>
+        <v>4544.229985010696</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4640.581756932947</v>
+        <v>4634.804653215277</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4715.653865500273</v>
+        <v>4706.463002113296</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4787.808855470877</v>
+        <v>4775.090514982638</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4859.23250232907</v>
+        <v>4841.853538020614</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4847.516025310391</v>
+        <v>4827.44229237512</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4787.802270482006</v>
+        <v>4766.00771340082</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4617.943631486554</v>
+        <v>4599.946589061938</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4478.261616451669</v>
+        <v>4462.77620142215</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4277.805366451669</v>
+        <v>4239.037568731469</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.487478762408</v>
+        <v>3669.517036465048</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.902326412856</v>
+        <v>3566.942455491176</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.669826528147</v>
+        <v>3512.716408063689</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.182049179727</v>
+        <v>3485.231752721415</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.724472602294</v>
+        <v>3493.775388693421</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.531147598255</v>
+        <v>3506.582662883101</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.036747115319</v>
+        <v>3521.0878741055</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.516801230265</v>
+        <v>3533.567107965049</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.148832534864</v>
+        <v>3549.186292676825</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.39241544577</v>
+        <v>3452.383053559718</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.023413587825</v>
+        <v>3450.015175689705</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.123410241222</v>
+        <v>3450.115802579845</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.398000189119</v>
+        <v>3531.357496051979</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.106190390408</v>
+        <v>3627.028176832418</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3777.65150079325</v>
+        <v>3777.532710023684</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3849.184581797456</v>
+        <v>3849.077914593129</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3896.127975162652</v>
+        <v>3896.02716842077</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.941738341883</v>
+        <v>3881.853893167086</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3886.028996820322</v>
+        <v>3885.991642304601</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.330513914111</v>
+        <v>3993.318009240733</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.167515044316</v>
+        <v>4067.130837519009</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.94794558981</v>
+        <v>4106.902733829624</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.279985235819</v>
+        <v>4206.275808760682</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.045987778699</v>
+        <v>4199.028221101343</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.61590956104</v>
+        <v>4222.56590948632</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.400923147472</v>
+        <v>4243.350010007008</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.345773240851</v>
+        <v>4307.273918027387</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4399.133126199129</v>
+        <v>4399.041839444408</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.921140720118</v>
+        <v>4434.821356641476</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4535.464155498706</v>
+        <v>4535.330145633138</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4670.019740445962</v>
+        <v>4669.857176066803</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4750.209749719545</v>
+        <v>4749.997138441364</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4889.328307208012</v>
+        <v>4889.205268260419</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4930.065357072504</v>
+        <v>4929.930066168643</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5035.177089661131</v>
+        <v>5034.999618235684</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5205.704306732665</v>
+        <v>5205.601755213491</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.717365950262</v>
+        <v>5250.695849868689</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5295.972879545438</v>
+        <v>5296.073703960034</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5376.155484554974</v>
+        <v>5376.350464661597</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5455.00319135779</v>
+        <v>5455.256699333568</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5586.101278082657</v>
+        <v>5586.379831026563</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5528.888214933178</v>
+        <v>5529.248151824905</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5357.276051522653</v>
+        <v>5357.727459900472</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5239.849703258281</v>
+        <v>5240.277888972993</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5107.198839283901</v>
+        <v>5107.66387523682</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4991.748134091339</v>
+        <v>4992.171603521306</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4888.457151716513</v>
+        <v>4888.865586790334</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4841.88132596692</v>
+        <v>4842.343475180915</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4710.11532290763</v>
+        <v>4710.485946699946</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4584.700447866428</v>
+        <v>4584.956935375705</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4485.58275529036</v>
+        <v>4485.74965849541</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4480.866381303775</v>
+        <v>4481.036785091291</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4402.584694767826</v>
+        <v>4402.799305810438</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4247.36819870781</v>
+        <v>4247.659311003886</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4152.025191493582</v>
+        <v>4152.276114237055</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4099.244001417636</v>
+        <v>4099.409134217021</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.891444728711</v>
+        <v>4081.900431887632</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4124.317682633819</v>
+        <v>4124.096946273026</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4201.552196462859</v>
+        <v>4201.067350189947</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4297.086461137024</v>
+        <v>4296.433540775679</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4340.80123768368</v>
+        <v>4340.146319427954</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4347.560935874893</v>
+        <v>4346.999767868527</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4341.459722644114</v>
+        <v>4341.755824501552</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4354.666429465867</v>
+        <v>4354.538728799663</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4403.144517715618</v>
+        <v>4402.65739295391</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4470.718926693156</v>
+        <v>4468.946871309561</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4544.229985010696</v>
+        <v>4540.891304133424</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4634.804653215277</v>
+        <v>4628.833474031921</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4706.463002113296</v>
+        <v>4697.406821320987</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4775.090514982638</v>
+        <v>4762.81133088161</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4841.853538020614</v>
+        <v>4825.294471696929</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4827.44229237512</v>
+        <v>4808.561659209605</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4766.00771340082</v>
+        <v>4745.954087445683</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4599.946589061938</v>
+        <v>4584.09510987787</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4462.77620142215</v>
+        <v>4450.714435779318</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4239.037568731469</v>
+        <v>4263.980656666638</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.517036465048</v>
+        <v>3669.546031215389</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.942455491176</v>
+        <v>3566.981822688838</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.716408063689</v>
+        <v>3512.762107777845</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.231752721415</v>
+        <v>3485.280518818617</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.775388693421</v>
+        <v>3493.82534433373</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.582662883101</v>
+        <v>3506.633206271841</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.0878741055</v>
+        <v>3521.1380364519</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.567107965049</v>
+        <v>3533.616465530555</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.186292676825</v>
+        <v>3549.223055249824</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.383053559718</v>
+        <v>3452.373872934534</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.015175689705</v>
+        <v>3450.007097684464</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.115802579845</v>
+        <v>3450.108342854198</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.357496051979</v>
+        <v>3531.317772548879</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3627.028176832418</v>
+        <v>3626.951661385362</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3777.532710023684</v>
+        <v>3777.416187426825</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3849.077914593129</v>
+        <v>3848.973278542879</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3896.02716842077</v>
+        <v>3895.928256487681</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.853893167086</v>
+        <v>3881.767687039334</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.991642304601</v>
+        <v>3885.954970810444</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.318009240733</v>
+        <v>3993.305725031305</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.130837519009</v>
+        <v>4067.094846618202</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.902733829624</v>
+        <v>4106.858369770816</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.275808760682</v>
+        <v>4206.271724863853</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.028221101343</v>
+        <v>4199.010814515283</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.56590948632</v>
+        <v>4222.516897060708</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.350010007008</v>
+        <v>4243.3000937245</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.273918027387</v>
+        <v>4307.203459636823</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4399.041839444408</v>
+        <v>4398.952313962194</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.821356641476</v>
+        <v>4434.723482162616</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4535.330145633138</v>
+        <v>4535.198682074849</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4669.857176066803</v>
+        <v>4669.697705387664</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4749.997138441364</v>
+        <v>4749.78848095273</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4889.205268260419</v>
+        <v>4889.084563313672</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4929.930066168643</v>
+        <v>4929.797340321829</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5034.999618235684</v>
+        <v>5034.825492086581</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5205.601755213491</v>
+        <v>5205.50108817002</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.695849868689</v>
+        <v>5250.674604587606</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.073703960034</v>
+        <v>5296.172436197023</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5376.350464661597</v>
+        <v>5376.541610268914</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5455.256699333568</v>
+        <v>5455.505240931931</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5586.379831026563</v>
+        <v>5586.652952055018</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5529.248151824905</v>
+        <v>5529.601185710584</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5357.727459900472</v>
+        <v>5358.170274927306</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5240.277888972993</v>
+        <v>5240.697972293296</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5107.66387523682</v>
+        <v>5108.120189420822</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4992.171603521306</v>
+        <v>4992.587185605833</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4888.865586790334</v>
+        <v>4889.266483452722</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4842.343475180915</v>
+        <v>4842.797099479034</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4710.485946699946</v>
+        <v>4710.849715405735</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4584.956935375705</v>
+        <v>4585.208625673923</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4485.74965849541</v>
+        <v>4485.913345555442</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4481.036785091291</v>
+        <v>4481.203909235077</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4402.799305810438</v>
+        <v>4403.009837098469</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4247.659311003886</v>
+        <v>4247.945006407611</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4152.276114237055</v>
+        <v>4152.522557339305</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4099.409134217021</v>
+        <v>4099.571474377412</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.900431887632</v>
+        <v>4081.9097051811</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4124.096946273026</v>
+        <v>4123.880890098386</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4201.067350189947</v>
+        <v>4200.591986400124</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4296.433540775679</v>
+        <v>4295.792772694213</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4340.146319427954</v>
+        <v>4339.502632515182</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4346.999767868527</v>
+        <v>4346.447371545979</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4341.755824501552</v>
+        <v>4342.267005912676</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4354.538728799663</v>
+        <v>4354.676389432452</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4402.65739295391</v>
+        <v>4402.428265938686</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4468.946871309561</v>
+        <v>4467.571547185647</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4540.891304133424</v>
+        <v>4538.052258082369</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4628.833474031921</v>
+        <v>4623.540646002632</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4697.406821320987</v>
+        <v>4689.268536602453</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4762.81133088161</v>
+        <v>4751.717337382175</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4825.294471696929</v>
+        <v>4810.36070773044</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4808.561659209605</v>
+        <v>4791.766347546754</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4745.954087445683</v>
+        <v>4728.566427970549</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4584.09510987787</v>
+        <v>4571.266050150612</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4450.714435779318</v>
+        <v>4442.820791190084</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4263.980656666638</v>
+        <v>4283.221505125706</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.546031215389</v>
+        <v>3669.574478944122</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3566.981822688838</v>
+        <v>3567.020449497635</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.762107777845</v>
+        <v>3512.806950472952</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.280518818617</v>
+        <v>3485.328373739136</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.82534433373</v>
+        <v>3493.874366439504</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.633206271841</v>
+        <v>3506.682805005538</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.1380364519</v>
+        <v>3521.187261194411</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.616465530555</v>
+        <v>3533.664900532991</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.223055249824</v>
+        <v>3549.259139546147</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.373872934534</v>
+        <v>3452.364868358425</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3450.007097684464</v>
+        <v>3449.999174963836</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.108342854198</v>
+        <v>3450.101026793056</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.317772548879</v>
+        <v>3531.278807334978</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.951661385362</v>
+        <v>3626.876601323405</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3777.416187426825</v>
+        <v>3777.301868677065</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.973278542879</v>
+        <v>3848.870616192289</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.928256487681</v>
+        <v>3895.831186470732</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.767687039334</v>
+        <v>3881.683074551317</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.954970810444</v>
+        <v>3885.9189638096</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.305725031305</v>
+        <v>3993.293655540303</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.094846618202</v>
+        <v>4067.059523242448</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.858369770816</v>
+        <v>4106.814829800334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.271724863853</v>
+        <v>4206.267730560375</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4199.010814515283</v>
+        <v>4198.993757230211</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.516897060708</v>
+        <v>4222.468843368662</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.3000937245</v>
+        <v>4243.251145368611</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.203459636823</v>
+        <v>4307.134357809446</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.952313962194</v>
+        <v>4398.864499361172</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.723482162616</v>
+        <v>4434.62746306171</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4535.198682074849</v>
+        <v>4535.069693012159</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4669.697705387664</v>
+        <v>4669.541241036861</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4749.78848095273</v>
+        <v>4749.583668111169</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4889.084563313672</v>
+        <v>4888.966126667823</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4929.797340321829</v>
+        <v>4929.667107365037</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5034.825492086581</v>
+        <v>5034.654617681546</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5205.50108817002</v>
+        <v>5205.402254265597</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.674604587606</v>
+        <v>5250.653626377676</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.172436197023</v>
+        <v>5296.269140222481</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5376.541610268914</v>
+        <v>5376.729033156851</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5455.505240931931</v>
+        <v>5455.748960362274</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5586.652952055018</v>
+        <v>5586.920798242265</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5529.601185710584</v>
+        <v>5529.947513047668</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5358.170274927306</v>
+        <v>5358.604739281886</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5240.697972293296</v>
+        <v>5241.110180645623</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5108.120189420822</v>
+        <v>5108.568024448581</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4992.587185605833</v>
+        <v>4992.995098302748</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4889.266483452722</v>
+        <v>4889.660048070406</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4842.797099479034</v>
+        <v>4843.242432063797</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4710.849715405735</v>
+        <v>4711.206817109323</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4585.208625673923</v>
+        <v>4585.455651909305</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4485.913345555442</v>
+        <v>4486.073908369693</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4481.203909235077</v>
+        <v>4481.367847366074</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4403.009837098469</v>
+        <v>4403.216403655355</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4247.945006407611</v>
+        <v>4248.225434204152</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4152.522557339305</v>
+        <v>4152.76463876808</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4099.571474377412</v>
+        <v>4099.731090933916</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.9097051811</v>
+        <v>4081.91924431609</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4123.880890098386</v>
+        <v>4123.669370541671</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4200.591986400124</v>
+        <v>4200.125834218586</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4295.792772694213</v>
+        <v>4295.163827315435</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4339.502632515182</v>
+        <v>4338.869900605278</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4346.447371545979</v>
+        <v>4345.903557490841</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4342.267005912676</v>
+        <v>4341.740260716633</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4354.676389432452</v>
+        <v>4353.349184197459</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4402.428265938686</v>
+        <v>4399.850785950963</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4467.571547185647</v>
+        <v>4463.755161857809</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4538.052258082369</v>
+        <v>4533.835382271833</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4623.540646002632</v>
+        <v>4617.174820921335</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4689.268536602453</v>
+        <v>4680.3167101328</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4751.717337382175</v>
+        <v>4740.03253399166</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4810.36070773044</v>
+        <v>4795.118315423013</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4791.766347546754</v>
+        <v>4774.915271061898</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4728.566427970549</v>
+        <v>4711.437281890325</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4571.266050150612</v>
+        <v>4558.560430261978</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4442.820791190084</v>
+        <v>4434.694215105966</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,15 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4283.221505125706</v>
+        <v>4293.707326748498</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B83">
+        <v>4334.879755989978</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.574478944122</v>
+        <v>3669.60239498649</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.020449497635</v>
+        <v>3567.058356608594</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.806950472952</v>
+        <v>3512.850960029969</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.328373739136</v>
+        <v>3485.375342778687</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.874366439504</v>
+        <v>3493.922480930793</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.682805005538</v>
+        <v>3506.73148531685</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.187261194411</v>
+        <v>3521.235574371891</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.664900532991</v>
+        <v>3533.712438593581</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.259139546147</v>
+        <v>3549.294564153652</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.364868358425</v>
+        <v>3452.356034817437</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.999174963836</v>
+        <v>3449.991403094876</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.101026793056</v>
+        <v>3450.093850287971</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.278807334978</v>
+        <v>3531.240578909899</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.876601323405</v>
+        <v>3626.802955529516</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3777.301868677065</v>
+        <v>3777.189691857575</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.870616192289</v>
+        <v>3848.769872233104</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.831186470732</v>
+        <v>3895.735907426513</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.683074551317</v>
+        <v>3881.600011956085</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.9189638096</v>
+        <v>3885.883603436622</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.293655540303</v>
+        <v>3993.281795218806</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.059523242448</v>
+        <v>4067.024848994073</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.814829800334</v>
+        <v>4106.772091173822</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.267730560375</v>
+        <v>4206.263822990357</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.993757230211</v>
+        <v>4198.977038881035</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.468843368662</v>
+        <v>4222.421720610293</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.251145368611</v>
+        <v>4243.203137114609</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.134357809446</v>
+        <v>4307.066573815173</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.864499361172</v>
+        <v>4398.778347150767</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.62746306171</v>
+        <v>4434.53324714772</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4535.069693012159</v>
+        <v>4534.94310930571</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4669.541241036861</v>
+        <v>4669.387698898107</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4749.583668111169</v>
+        <v>4749.382594749863</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.966126667823</v>
+        <v>4888.849895062604</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4929.667107365037</v>
+        <v>4929.53929780973</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5034.654617681546</v>
+        <v>5034.48690493664</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5205.402254265597</v>
+        <v>5205.305204006396</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.653626377676</v>
+        <v>5250.63291150215</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.269140222481</v>
+        <v>5296.363877437707</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5376.729033156851</v>
+        <v>5376.912840810819</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5455.748960362274</v>
+        <v>5455.987996315654</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5586.920798242265</v>
+        <v>5587.183520674283</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5529.947513047668</v>
+        <v>5530.287322917572</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5358.604739281886</v>
+        <v>5359.03108660476</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5241.110180645623</v>
+        <v>5241.514733038335</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5108.568024448581</v>
+        <v>5109.007614034607</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4992.995098302748</v>
+        <v>4993.395551626106</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4889.660048070406</v>
+        <v>4890.046479561652</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4843.242432063797</v>
+        <v>4843.67969772815</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4711.206817109323</v>
+        <v>4711.557433090105</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4585.455651909305</v>
+        <v>4585.69814235488</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4486.073908369693</v>
+        <v>4486.231435375454</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4481.367847366074</v>
+        <v>4481.528689590089</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4403.216403655355</v>
+        <v>4403.41911622877</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4248.225434204152</v>
+        <v>4248.500738262084</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4152.76463876808</v>
+        <v>4153.002472420469</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4099.731090933916</v>
+        <v>4099.888050712692</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.91924431609</v>
+        <v>4081.929030182853</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4123.669370541671</v>
+        <v>4123.462249727752</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4200.125834218586</v>
+        <v>4199.668632829064</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4295.163827315435</v>
+        <v>4294.546386634164</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4338.869900605278</v>
+        <v>4338.24785595464</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4345.903557490841</v>
+        <v>4345.368141081816</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4341.740260716633</v>
+        <v>4341.220951218167</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4353.349184197459</v>
+        <v>4351.838231790846</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4399.850785950963</v>
+        <v>4397.05991379883</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4463.755161857809</v>
+        <v>4459.656698855444</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4533.835382271833</v>
+        <v>4529.372352162524</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4617.174820921335</v>
+        <v>4610.664937907019</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4680.3167101328</v>
+        <v>4671.347369418615</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4740.03253399166</v>
+        <v>4728.473085728894</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4795.118315423013</v>
+        <v>4780.220518336775</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4774.915271061898</v>
+        <v>4758.567747643646</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4711.437281890325</v>
+        <v>4694.934290789607</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4558.560430261978</v>
+        <v>4546.197745257505</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4434.694215105966</v>
+        <v>4426.3892032908</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4293.707326748498</v>
+        <v>4298.566705937443</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4334.879755989978</v>
+        <v>4325.822891911011</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.60239498649</v>
+        <v>3669.629794109849</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.058356608594</v>
+        <v>3567.095563948933</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.850960029969</v>
+        <v>3512.894159450871</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.375342778687</v>
+        <v>3485.421450305436</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.922480930793</v>
+        <v>3493.969712777068</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.73148531685</v>
+        <v>3506.77927247625</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.235574371891</v>
+        <v>3521.283001068047</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.712438593581</v>
+        <v>3533.759104393715</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.294564153652</v>
+        <v>3549.329346987599</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.356034817437</v>
+        <v>3452.347367486156</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.991403094876</v>
+        <v>3449.98377781171</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.093850287971</v>
+        <v>3450.086809385596</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.240578909899</v>
+        <v>3531.203066578229</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.802955529516</v>
+        <v>3626.730684420482</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3777.189691857575</v>
+        <v>3777.079597348644</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.769872233104</v>
+        <v>3848.670993403965</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.735907426513</v>
+        <v>3895.642370271941</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.600011956085</v>
+        <v>3881.518457091919</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.883603436622</v>
+        <v>3885.848872459557</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.281795218806</v>
+        <v>3993.270138706219</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4067.024848994073</v>
+        <v>4066.99080614523</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.772091173822</v>
+        <v>4106.730131976046</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.263822990357</v>
+        <v>4206.259999412572</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.977038881035</v>
+        <v>4198.960649507204</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.421720610293</v>
+        <v>4222.375502048157</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.203137114609</v>
+        <v>4243.156042192057</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.066573815173</v>
+        <v>4307.000070381715</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.778347150767</v>
+        <v>4398.693810652504</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.53324714772</v>
+        <v>4434.440784166343</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.94310930571</v>
+        <v>4534.81886436543</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4669.387698898107</v>
+        <v>4669.236997960483</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4749.382594749863</v>
+        <v>4749.185159498469</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.849895062604</v>
+        <v>4888.73580756537</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4929.53929780973</v>
+        <v>4929.413844722911</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5034.48690493664</v>
+        <v>5034.322267059082</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5205.305204006396</v>
+        <v>5205.209889659704</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.63291150215</v>
+        <v>5250.612456223973</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.363877437707</v>
+        <v>5296.456706805806</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5376.912840810819</v>
+        <v>5377.093136625623</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5455.987996315654</v>
+        <v>5456.222482225718</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5587.183520674283</v>
+        <v>5587.441264731016</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5530.287322917572</v>
+        <v>5530.620797368227</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5359.03108660476</v>
+        <v>5359.449541914533</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5241.514733038335</v>
+        <v>5241.911840446977</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5109.007614034607</v>
+        <v>5109.43918339867</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4993.395551626106</v>
+        <v>4993.788748004192</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4890.046479561652</v>
+        <v>4890.425969728573</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4843.67969772815</v>
+        <v>4844.10911323026</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4711.557433090105</v>
+        <v>4711.90173812692</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4585.69814235488</v>
+        <v>4585.936220629262</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4486.231435375454</v>
+        <v>4486.386011709296</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4481.528689590089</v>
+        <v>4481.686522651909</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4403.41911622877</v>
+        <v>4403.618081487117</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4248.500738262084</v>
+        <v>4248.771057275968</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4153.002472420469</v>
+        <v>4153.236168295307</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4099.888050712692</v>
+        <v>4100.042418416217</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.929030182853</v>
+        <v>4081.939044782052</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4123.462249727752</v>
+        <v>4123.259395200069</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4199.668632829064</v>
+        <v>4199.220131018328</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4294.546386634164</v>
+        <v>4293.940143724743</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4338.24785595464</v>
+        <v>4337.636239104248</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4345.368141081816</v>
+        <v>4344.840942376819</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4341.220951218167</v>
+        <v>4340.708939134751</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4351.838231790846</v>
+        <v>4349.06964430036</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4397.05991379883</v>
+        <v>4392.743234746142</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4459.656698855444</v>
+        <v>4453.577894660104</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4529.372352162524</v>
+        <v>4523.194120884494</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4610.664937907019</v>
+        <v>4601.859610880281</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4671.347369418615</v>
+        <v>4659.972167167343</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4728.473085728894</v>
+        <v>4714.391046362318</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4780.220518336775</v>
+        <v>4762.569764700298</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4758.567747643646</v>
+        <v>4739.010252546967</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4694.934290789607</v>
+        <v>4674.476358739144</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4546.197745257505</v>
+        <v>4528.315576274309</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4426.3892032908</v>
+        <v>4409.308271982578</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4298.566705937443</v>
+        <v>4284.79921166156</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4325.822891911011</v>
+        <v>4275.994626352111</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.629794109849</v>
+        <v>3669.656690539707</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.095563948933</v>
+        <v>3567.132090716974</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.894159450871</v>
+        <v>3512.936570898707</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.421450305436</v>
+        <v>3485.466719802116</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3493.969712777068</v>
+        <v>3494.016086040399</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.77927247625</v>
+        <v>3506.826190835735</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.283001068047</v>
+        <v>3521.329565454826</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.759104393715</v>
+        <v>3533.804921717641</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.329346987599</v>
+        <v>3549.363505320783</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.347367486156</v>
+        <v>3452.338861718934</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.98377781171</v>
+        <v>3449.976295007737</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.086809385596</v>
+        <v>3450.079900280433</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.203066578229</v>
+        <v>3531.166250412198</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.730684420482</v>
+        <v>3626.659749876066</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3777.079597348644</v>
+        <v>3776.971527722148</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.670993403965</v>
+        <v>3848.573928396611</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.642370271941</v>
+        <v>3895.550527700155</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.518457091919</v>
+        <v>3881.438369311234</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.848872459557</v>
+        <v>3885.814754252165</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.270138706219</v>
+        <v>3993.25868082241</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.99080614523</v>
+        <v>4066.957377607711</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.730131976046</v>
+        <v>4106.688931083462</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.259999412572</v>
+        <v>4206.256257198438</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.960649507204</v>
+        <v>4198.944579533235</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.375502048157</v>
+        <v>4222.330161957074</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.156042192057</v>
+        <v>4243.109834835441</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4307.000070381715</v>
+        <v>4306.934811626743</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.693810652504</v>
+        <v>4398.610844916298</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.440784166343</v>
+        <v>4434.350025711106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.81886436543</v>
+        <v>4534.696894034239</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4669.236997960483</v>
+        <v>4669.089060176595</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4749.185159498469</v>
+        <v>4748.99126461355</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.73580756537</v>
+        <v>4888.623805465159</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4929.413844722911</v>
+        <v>4929.290683610852</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5034.322267059082</v>
+        <v>5034.160620398573</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5205.209889659704</v>
+        <v>5205.116265176507</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.612456223973</v>
+        <v>5250.592256812147</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.456706805806</v>
+        <v>5296.547684970868</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5377.093136625623</v>
+        <v>5377.270020097886</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5456.222482225718</v>
+        <v>5456.452546515023</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5587.441264731016</v>
+        <v>5587.694170352801</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5530.620797368227</v>
+        <v>5530.948111737744</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5359.449541914533</v>
+        <v>5359.860322001336</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5241.911840446977</v>
+        <v>5242.3017061786</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5109.43918339867</v>
+        <v>5109.862949647526</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4993.788748004192</v>
+        <v>4994.174882618384</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4890.425969728573</v>
+        <v>4890.798703571847</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4844.10911323026</v>
+        <v>4844.530887648483</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4711.90173812692</v>
+        <v>4712.239900786277</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4585.936220629262</v>
+        <v>4586.170005905558</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4486.386011709296</v>
+        <v>4486.537719359367</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4481.686522651909</v>
+        <v>4481.841430090336</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4403.618081487117</v>
+        <v>4403.813402205298</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4248.771057275968</v>
+        <v>4249.036524996056</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4153.236168295307</v>
+        <v>4153.465832656972</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4100.042418416217</v>
+        <v>4100.194256704778</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.939044782052</v>
+        <v>4081.949271156808</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4123.259395200069</v>
+        <v>4123.060679661582</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4199.220131018328</v>
+        <v>4198.78008674482</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4293.940143724743</v>
+        <v>4293.344802272852</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4337.636239104248</v>
+        <v>4337.034798580018</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4344.840942376819</v>
+        <v>4344.321785997763</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4340.708939134751</v>
+        <v>4340.204088798375</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4349.06964430036</v>
+        <v>4346.427647182894</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4392.743234746142</v>
+        <v>4388.787865684586</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4453.577894660104</v>
+        <v>4448.296219634549</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4523.194120884494</v>
+        <v>4519.052099443355</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4601.859610880281</v>
+        <v>4593.44898581786</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4659.972167167343</v>
+        <v>4649.143759554701</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4714.391046362318</v>
+        <v>4701.025570984994</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4762.569764700298</v>
+        <v>4745.913696510972</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4739.010252546967</v>
+        <v>4720.710327357972</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4674.476358739144</v>
+        <v>4655.572723499374</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4528.315576274309</v>
+        <v>4512.12468864547</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4409.308271982578</v>
+        <v>4394.54561127482</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4284.79921166156</v>
+        <v>4274.108086783788</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4275.994626352111</v>
+        <v>4251.093370792132</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4346.427647182894</v>
+        <v>4347.503863659505</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4388.787865684586</v>
+        <v>4390.013316320412</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4448.296219634549</v>
+        <v>4449.646283956344</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4519.052099443355</v>
+        <v>4520.432724625889</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4593.44898581786</v>
+        <v>4595.291826711284</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4649.143759554701</v>
+        <v>4651.271196911683</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4701.025570984994</v>
+        <v>4703.442338506069</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4745.913696510972</v>
+        <v>4748.771577015903</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4720.710327357972</v>
+        <v>4724.151126317383</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4655.572723499374</v>
+        <v>4659.811298640443</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4512.12468864547</v>
+        <v>4517.559686251773</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4394.54561127482</v>
+        <v>4402.466301928016</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4274.108086783788</v>
+        <v>4287.332739700538</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4251.093370792132</v>
+        <v>4281.229469148363</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.656690539707</v>
+        <v>3669.683097984353</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.132090716974</v>
+        <v>3567.167955415172</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.936570898707</v>
+        <v>3512.978215735504</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.466719802116</v>
+        <v>3485.511173905877</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.016086040399</v>
+        <v>3494.061623916291</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.826190835735</v>
+        <v>3506.872263870171</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.329565454826</v>
+        <v>3521.37529083346</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.804921717641</v>
+        <v>3533.849913492854</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.363505320783</v>
+        <v>3549.397055812055</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.338861718934</v>
+        <v>3452.330513041597</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.976295007737</v>
+        <v>3449.968950728269</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.079900280433</v>
+        <v>3450.073119307995</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.166250412198</v>
+        <v>3531.130111216435</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.659749876066</v>
+        <v>3626.590115172073</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.971527722148</v>
+        <v>3776.865427641812</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.573928396611</v>
+        <v>3848.478627767185</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.550527700155</v>
+        <v>3895.460334100945</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.438369311234</v>
+        <v>3881.359709413277</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.814754252165</v>
+        <v>3885.781232767598</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.25868082241</v>
+        <v>3993.247416560236</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.957377607711</v>
+        <v>4066.924546904342</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.688931083462</v>
+        <v>4106.648468128793</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.256257198438</v>
+        <v>4206.252593826347</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.944579533235</v>
+        <v>4198.928819750338</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.330161957074</v>
+        <v>4222.285675576759</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.109834835441</v>
+        <v>4243.064490237538</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.934811626743</v>
+        <v>4306.870762993799</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.610844916298</v>
+        <v>4398.52940664132</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.350025711106</v>
+        <v>4434.260925139321</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.696894034239</v>
+        <v>4534.57713647804</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4669.089060176595</v>
+        <v>4668.943810328462</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4748.99126461355</v>
+        <v>4748.800815817993</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.623805465159</v>
+        <v>4888.513832172483</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4929.290683610852</v>
+        <v>4929.16975230913</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5034.160620398573</v>
+        <v>5034.001884306603</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5205.116265176507</v>
+        <v>5205.0242861181</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.592256812147</v>
+        <v>5250.57230954739</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.547684970868</v>
+        <v>5296.636866370256</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5377.270020097886</v>
+        <v>5377.443587007721</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5456.452546515023</v>
+        <v>5456.678312827651</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5587.694170352801</v>
+        <v>5587.942372292044</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5530.948111737744</v>
+        <v>5531.269434960384</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5359.860322001336</v>
+        <v>5360.263635798987</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5242.3017061786</v>
+        <v>5242.684526216466</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5109.862949647526</v>
+        <v>5110.279122136287</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4994.174882618384</v>
+        <v>4994.554143724038</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4890.798703571847</v>
+        <v>4891.164859588916</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4844.530887648483</v>
+        <v>4844.945222717744</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4712.239900786277</v>
+        <v>4712.572083695402</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4586.170005905558</v>
+        <v>4586.399613109158</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4486.537719359367</v>
+        <v>4486.686637309354</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4481.841430090336</v>
+        <v>4481.993492384731</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4403.813402205298</v>
+        <v>4404.005177440446</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4249.036524996056</v>
+        <v>4249.297270445926</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4153.465832656972</v>
+        <v>4153.691568191103</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4100.194256704778</v>
+        <v>4100.343626274378</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.949271156808</v>
+        <v>4081.959693329291</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4123.060679661582</v>
+        <v>4122.865980730231</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4198.78008674482</v>
+        <v>4198.348266730007</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4293.344802272852</v>
+        <v>4292.760076130332</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4337.034798580018</v>
+        <v>4336.443290604935</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4344.321785997763</v>
+        <v>4343.810501016393</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4340.204088798375</v>
+        <v>4339.706267142655</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4347.503863659505</v>
+        <v>4346.012203663548</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4390.013316320412</v>
+        <v>4387.406523028261</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4449.646283956344</v>
+        <v>4445.888200211269</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4520.432724625889</v>
+        <v>4517.795645473308</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4595.291826711284</v>
+        <v>4589.021034648387</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4651.271196911683</v>
+        <v>4642.985448841374</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4703.442338506069</v>
+        <v>4693.042214492501</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4748.771577015903</v>
+        <v>4735.734214929295</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4724.151126317383</v>
+        <v>4710.222168783636</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4659.811298640443</v>
+        <v>4646.223978636239</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4517.559686251773</v>
+        <v>4507.77890851011</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4402.466301928016</v>
+        <v>4396.496379644754</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4287.332739700538</v>
+        <v>4289.355843855405</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4281.229469148363</v>
+        <v>4284.367431935886</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.683097984353</v>
+        <v>3669.709029658157</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.167955415172</v>
+        <v>3567.203175881357</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.978215735504</v>
+        <v>3513.019114558123</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.511173905877</v>
+        <v>3485.554834445998</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.061623916291</v>
+        <v>3494.106348772337</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.872263870171</v>
+        <v>3506.917514216417</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.37529083346</v>
+        <v>3521.420199673311</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.849913492854</v>
+        <v>3533.894101828321</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.397055812055</v>
+        <v>3549.430014533355</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.330513041597</v>
+        <v>3452.32231714361</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.968950728269</v>
+        <v>3449.961741163574</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.073119307995</v>
+        <v>3450.06646293833</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.130111216435</v>
+        <v>3531.094630494626</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.590115172073</v>
+        <v>3626.52174491703</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.865427641812</v>
+        <v>3776.761243768845</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.478627767185</v>
+        <v>3848.385043852333</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.460334100945</v>
+        <v>3895.371745485412</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.359709413277</v>
+        <v>3881.282439580379</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.781232767598</v>
+        <v>3885.74829251343</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.247416560236</v>
+        <v>3993.236341078434</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.924546904342</v>
+        <v>4066.892298141928</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.648468128793</v>
+        <v>4106.608723467499</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.252593826347</v>
+        <v>4206.249006876353</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.928819750338</v>
+        <v>4198.913361299088</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.285675576759</v>
+        <v>4222.242019067084</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.064490237538</v>
+        <v>4243.019984505348</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.870762993799</v>
+        <v>4306.807891191727</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.52940664132</v>
+        <v>4398.449454101158</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.260925139321</v>
+        <v>4434.173437492573</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.57713647804</v>
+        <v>4534.459532081635</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4668.943810328462</v>
+        <v>4668.801175900584</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4748.800815817993</v>
+        <v>4748.613722148875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.513832172483</v>
+        <v>4888.405833124471</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4929.16975230913</v>
+        <v>4929.050990878526</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5034.001884306603</v>
+        <v>5033.845981003215</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5205.0242861181</v>
+        <v>5204.933909586498</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.57230954739</v>
+        <v>5250.552610727176</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.636866370256</v>
+        <v>5296.724303340468</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5377.443587007721</v>
+        <v>5377.613929590347</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5456.678312827651</v>
+        <v>5456.899900249002</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5587.942372292044</v>
+        <v>5588.186000351059</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5531.269434960384</v>
+        <v>5531.584929855951</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5360.263635798987</v>
+        <v>5360.65968473714</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5242.684526216466</v>
+        <v>5243.06048954636</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5110.279122136287</v>
+        <v>5110.687902810678</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4994.554143724038</v>
+        <v>4994.926712954491</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4891.164859588916</v>
+        <v>4891.524610056659</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4844.945222717744</v>
+        <v>4845.352313148409</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4712.572083695402</v>
+        <v>4712.898443801059</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4586.399613109158</v>
+        <v>4586.625153105038</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4486.686637309354</v>
+        <v>4486.832841674632</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4481.993492384731</v>
+        <v>4482.142787093614</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4404.005177440446</v>
+        <v>4404.193502698236</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4249.297270445926</v>
+        <v>4249.553418128741</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4153.691568191103</v>
+        <v>4153.913474152645</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4100.343626274378</v>
+        <v>4100.490585931219</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.959693329291</v>
+        <v>4081.970296241532</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4122.865980730231</v>
+        <v>4122.675180707961</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4198.348266730007</v>
+        <v>4197.924446071052</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4292.760076130332</v>
+        <v>4292.185688891701</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4336.443290604935</v>
+        <v>4335.861478822524</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4343.810501016393</v>
+        <v>4343.306920841346</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4339.706267142655</v>
+        <v>4339.215343685413</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4346.012203663548</v>
+        <v>4344.100530608993</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4387.406523028261</v>
+        <v>4384.299111448945</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4445.888200211269</v>
+        <v>4441.610421201878</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4517.795645473308</v>
+        <v>4514.643198434056</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4589.021034648387</v>
+        <v>4582.137289866377</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4642.985448841374</v>
+        <v>4634.058055019837</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4693.042214492501</v>
+        <v>4681.98225309815</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4735.734214929295</v>
+        <v>4722.016600228588</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4710.222168783636</v>
+        <v>4695.481160788508</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4646.223978636239</v>
+        <v>4631.569177832824</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4507.77890851011</v>
+        <v>4496.274164906556</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4396.496379644754</v>
+        <v>4387.613457736257</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4289.355843855405</v>
+        <v>4285.35963980909</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4284.367431935886</v>
+        <v>4275.918491341466</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.709029658157</v>
+        <v>3669.734498303606</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.203175881357</v>
+        <v>3567.237769318303</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.019114558123</v>
+        <v>3513.059287232209</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.554834445998</v>
+        <v>3485.597722479602</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.106348772337</v>
+        <v>3494.150282184822</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.917514216417</v>
+        <v>3506.961963710389</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.420199673311</v>
+        <v>3521.464313648664</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.894101828321</v>
+        <v>3533.93750805068</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.430014533355</v>
+        <v>3549.462396995295</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.32231714361</v>
+        <v>3452.314269870662</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.961741163574</v>
+        <v>3449.954662642295</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.06646293833</v>
+        <v>3450.059927769912</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.094630494626</v>
+        <v>3531.059790417996</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.52174491703</v>
+        <v>3626.454604992303</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.761243768845</v>
+        <v>3776.658924672649</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.385043852333</v>
+        <v>3848.29313068979</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.371745485412</v>
+        <v>3895.284719414598</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.282439580379</v>
+        <v>3881.206523317541</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.74829251343</v>
+        <v>3885.71591852796</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.236341078434</v>
+        <v>3993.225449694854</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.892298141928</v>
+        <v>4066.860615985612</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.608723467499</v>
+        <v>4106.569678146007</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.249006876353</v>
+        <v>4206.245494025145</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.913361299088</v>
+        <v>4198.898195653069</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.242019067084</v>
+        <v>4222.199169465788</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.019984505348</v>
+        <v>4242.976294618451</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.807891191727</v>
+        <v>4306.74616413737</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.449454101158</v>
+        <v>4398.370947073035</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.173437492573</v>
+        <v>4434.087519421469</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.459532081635</v>
+        <v>4534.344023350177</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4668.801175900584</v>
+        <v>4668.661086959784</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4748.613722148875</v>
+        <v>4748.429895813269</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.405833124471</v>
+        <v>4888.29975569507</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4929.050990878526</v>
+        <v>4928.934341506471</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5033.845981003215</v>
+        <v>5033.692835450824</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.933909586498</v>
+        <v>5204.845094158414</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.552610727176</v>
+        <v>5250.533156670208</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.724303340468</v>
+        <v>5296.810046216997</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5377.613929590347</v>
+        <v>5377.781136698324</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5456.899900249002</v>
+        <v>5457.117423513592</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5588.186000351059</v>
+        <v>5588.425179606968</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5531.584929855951</v>
+        <v>5531.894753403658</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5360.65968473714</v>
+        <v>5361.048663074727</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5243.06048954636</v>
+        <v>5243.429778465638</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5110.687902810678</v>
+        <v>5111.089486531355</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4994.926712954491</v>
+        <v>4995.292765609234</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4891.524610056659</v>
+        <v>4891.878121299497</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4845.352313148409</v>
+        <v>4845.752346928734</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4712.898443801059</v>
+        <v>4713.219132614947</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4586.625153105038</v>
+        <v>4586.846732875287</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4486.832841674632</v>
+        <v>4486.976405831083</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4482.142787093614</v>
+        <v>4482.289388985795</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4404.193502698236</v>
+        <v>4404.378470090369</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4249.553418128741</v>
+        <v>4249.805088222853</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4153.913474152645</v>
+        <v>4154.131646506698</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4100.490585931219</v>
+        <v>4100.635192662937</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.970296241532</v>
+        <v>4081.981065700146</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4122.675180707961</v>
+        <v>4122.488166362456</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4197.924446071052</v>
+        <v>4197.508407873581</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4292.185688891701</v>
+        <v>4291.621373491193</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4335.861478822524</v>
+        <v>4335.28913403122</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4343.306920841346</v>
+        <v>4342.810883106702</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4339.215343685413</v>
+        <v>4338.731190507289</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4344.100530608993</v>
+        <v>4343.744507242602</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4384.299111448945</v>
+        <v>4378.244597967418</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4441.610421201878</v>
+        <v>4433.286763321748</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4514.643198434056</v>
+        <v>4503.58143773299</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4582.137289866377</v>
+        <v>4567.966235441529</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4634.058055019837</v>
+        <v>4617.140466274015</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4681.98225309815</v>
+        <v>4662.509066761803</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4722.016600228588</v>
+        <v>4699.011230555891</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4695.481160788508</v>
+        <v>4670.022102494739</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4631.569177832824</v>
+        <v>4604.666671072144</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4496.274164906556</v>
+        <v>4469.425334110583</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4387.613457736257</v>
+        <v>4357.45971277384</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4285.35963980909</v>
+        <v>4248.872129405871</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,15 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4275.918491341466</v>
+        <v>4212.594468957794</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B84">
+        <v>4015.040718957794</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.734498303606</v>
+        <v>3669.759516212188</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.237769318303</v>
+        <v>3567.271752321746</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.059287232209</v>
+        <v>3513.09875292436</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.597722479602</v>
+        <v>3485.639858325485</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.150282184822</v>
+        <v>3494.193444973408</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.961963710389</v>
+        <v>3507.005633422164</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.464313648664</v>
+        <v>3521.507653673577</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.93750805068</v>
+        <v>3533.980152738533</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.462396995295</v>
+        <v>3549.494218171455</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.314269870662</v>
+        <v>3452.306367217655</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.954662642295</v>
+        <v>3449.947711625227</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.059927769912</v>
+        <v>3450.053510523851</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.059790417996</v>
+        <v>3531.02557379547</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.454604992303</v>
+        <v>3626.388662495406</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.658924672649</v>
+        <v>3776.558420746263</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.29313068979</v>
+        <v>3848.202843943176</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.284719414598</v>
+        <v>3895.199214931858</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.206523317541</v>
+        <v>3881.13192539516</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.71591852796</v>
+        <v>3885.684096357723</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.225449694854</v>
+        <v>3993.214737880019</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.860615985612</v>
+        <v>4066.829485634565</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.569678146007</v>
+        <v>4106.531313871601</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.245494025145</v>
+        <v>4206.242053041333</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.898195653069</v>
+        <v>4198.883314603416</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.199169465788</v>
+        <v>4222.157104648519</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.976294618451</v>
+        <v>4242.933398389587</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.74616413737</v>
+        <v>4306.685550901366</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.370947073035</v>
+        <v>4398.293846770775</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.087519421469</v>
+        <v>4434.00312911438</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.344023350177</v>
+        <v>4534.230554815815</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4668.661086959784</v>
+        <v>4668.523476041406</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4748.429895813269</v>
+        <v>4748.249252051495</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.29975569507</v>
+        <v>4888.195549109965</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4928.934341506471</v>
+        <v>4928.819748413664</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5033.692835450824</v>
+        <v>5033.542375234598</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.845094158414</v>
+        <v>5204.757799822599</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.533156670208</v>
+        <v>5250.513943720374</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.810046216997</v>
+        <v>5296.894143428553</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5377.781136698324</v>
+        <v>5377.945293954948</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5457.117423513592</v>
+        <v>5457.330993201618</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5588.425179606968</v>
+        <v>5588.66003062446</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5531.894753403658</v>
+        <v>5532.199057001408</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5361.048663074727</v>
+        <v>5361.430758215765</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5243.429778465638</v>
+        <v>5243.792568876052</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5111.089486531355</v>
+        <v>5111.484061381364</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4995.292765609234</v>
+        <v>4995.652470927178</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4891.878121299497</v>
+        <v>4892.225553943759</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4845.752346928734</v>
+        <v>4846.145505611866</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4713.219132614947</v>
+        <v>4713.534296446533</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4586.846732875287</v>
+        <v>4587.064455687395</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4486.976405831083</v>
+        <v>4487.117400537049</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4482.289388985795</v>
+        <v>4482.433370164519</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4404.378470090369</v>
+        <v>4404.560168483758</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4249.805088222853</v>
+        <v>4250.052396767365</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4154.131646506698</v>
+        <v>4154.346178062545</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4100.635192662937</v>
+        <v>4100.777501706722</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.981065700146</v>
+        <v>4081.99198832467</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4122.488166362456</v>
+        <v>4122.304828720793</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4197.508407873581</v>
+        <v>4197.099942903298</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4291.621373491193</v>
+        <v>4291.066871819194</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4335.28913403122</v>
+        <v>4334.726033929189</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4342.810883106702</v>
+        <v>4342.322229562174</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4338.731190507289</v>
+        <v>4338.253682226901</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4343.744507242602</v>
+        <v>4343.392546759644</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4378.244597967418</v>
+        <v>4373.175120395275</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4433.286763321748</v>
+        <v>4426.091430787974</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4503.58143773299</v>
+        <v>4493.815611460902</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4567.966235441529</v>
+        <v>4555.326862780068</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4617.140466274015</v>
+        <v>4601.982609887429</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4662.509066761803</v>
+        <v>4645.033409072681</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4699.011230555891</v>
+        <v>4678.441352562921</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4670.022102494739</v>
+        <v>4647.527232560686</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4604.666671072144</v>
+        <v>4580.795033337938</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4469.425334110583</v>
+        <v>4447.348250268005</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4357.45971277384</v>
+        <v>4334.118440962688</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4248.872129405871</v>
+        <v>4223.265472630228</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4212.594468957794</v>
+        <v>4173.676846108394</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>4015.040718957794</v>
+        <v>3978.879346108394</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4373.175120395275</v>
+        <v>4373.099486758167</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4426.091430787974</v>
+        <v>4426.004124259025</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4493.815611460902</v>
+        <v>4493.710255038471</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4555.326862780068</v>
+        <v>4555.898536738128</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4601.982609887429</v>
+        <v>4602.26334190556</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4645.033409072681</v>
+        <v>4645.145854345303</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4678.441352562921</v>
+        <v>4678.41575149118</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4647.527232560686</v>
+        <v>4647.373782447011</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4580.795033337938</v>
+        <v>4580.511221402512</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4447.348250268005</v>
+        <v>4447.191668260642</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4334.118440962688</v>
+        <v>4333.852925217973</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4223.265472630228</v>
+        <v>4222.827335969277</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4173.676846108394</v>
+        <v>4172.905873047005</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3978.879346108394</v>
+        <v>3978.108373047005</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.759516212188</v>
+        <v>3669.784095244165</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.271752321746</v>
+        <v>3567.305140906919</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.09875292436</v>
+        <v>3513.137530132589</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.639858325485</v>
+        <v>3485.681261596198</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.193444973408</v>
+        <v>3494.235857233998</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3507.005633422164</v>
+        <v>3507.048543689254</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.507653673577</v>
+        <v>3521.550239934912</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.980152738533</v>
+        <v>3534.022055754949</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.494218171455</v>
+        <v>3549.525492521406</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.306367217655</v>
+        <v>3452.298605322072</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.947711625227</v>
+        <v>3449.940884699431</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.053510523851</v>
+        <v>3450.047208038422</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.02557379547</v>
+        <v>3530.991964045421</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.388662495406</v>
+        <v>3626.323885686304</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.558420746263</v>
+        <v>3776.459684126276</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.202843943176</v>
+        <v>3848.114140830751</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.199214931858</v>
+        <v>3895.115192498743</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.13192539516</v>
+        <v>3881.0586117947</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.684096357723</v>
+        <v>3885.652812036139</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.214737880019</v>
+        <v>3993.204201250999</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.829485634565</v>
+        <v>4066.798892798948</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.531313871601</v>
+        <v>4106.493612983875</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.242053041333</v>
+        <v>4206.238681780989</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.883314603416</v>
+        <v>4198.868710244219</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.157104648519</v>
+        <v>4222.115803291013</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.933398389587</v>
+        <v>4242.891274427368</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.685550901366</v>
+        <v>4306.626021656817</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.293846770775</v>
+        <v>4398.218115781337</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.00312911438</v>
+        <v>4433.920226229937</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.230554815815</v>
+        <v>4534.119072949237</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4668.523476041406</v>
+        <v>4668.388278041461</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4748.249252051495</v>
+        <v>4748.071709007386</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.195549109965</v>
+        <v>4888.093164365931</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4928.819748413664</v>
+        <v>4928.707157765572</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5033.542375234598</v>
+        <v>5033.394530449043</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.757799822599</v>
+        <v>5204.671987920327</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.513943720374</v>
+        <v>5250.494968250243</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.894143428553</v>
+        <v>5296.976641586059</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5377.945293954948</v>
+        <v>5378.106483899388</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5457.330993201618</v>
+        <v>5457.540715924953</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5588.66003062446</v>
+        <v>5588.890669657181</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5532.199057001408</v>
+        <v>5532.497986711407</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5361.430758215765</v>
+        <v>5361.806151008663</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5243.792568876052</v>
+        <v>5244.149030561372</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5111.484061381364</v>
+        <v>5111.871808957761</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4995.652470927178</v>
+        <v>4996.005992345924</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4892.225553943759</v>
+        <v>4892.567063159153</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4846.145505611866</v>
+        <v>4846.531964588268</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4713.534296446533</v>
+        <v>4713.844076624035</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4587.064455687395</v>
+        <v>4587.278421253874</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4487.117400537049</v>
+        <v>4487.255894048839</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4482.433370164519</v>
+        <v>4482.574800185045</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4404.560168483758</v>
+        <v>4404.738683641927</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4250.052396767365</v>
+        <v>4250.295455838254</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4154.346178062545</v>
+        <v>4154.557158601238</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4100.777501706722</v>
+        <v>4100.917566614515</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4081.99198832467</v>
+        <v>4082.00305149928</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4122.304828720793</v>
+        <v>4122.125062874262</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4197.099942903298</v>
+        <v>4196.69884925541</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4291.066871819194</v>
+        <v>4290.521934357027</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4334.726033929189</v>
+        <v>4334.171962869224</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4342.322229562174</v>
+        <v>4341.840805965101</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4338.253682226901</v>
+        <v>4337.78269597301</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4343.392546759644</v>
+        <v>4343.044598574639</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4373.099486758167</v>
+        <v>4368.108370096882</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4426.004124259025</v>
+        <v>4418.956773844617</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4493.710255038471</v>
+        <v>4484.177394340879</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4555.898536738128</v>
+        <v>4544.264819024231</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4602.26334190556</v>
+        <v>4587.9656268239</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4645.145854345303</v>
+        <v>4628.50064578802</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4678.41575149118</v>
+        <v>4658.761984799687</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4647.373782447011</v>
+        <v>4625.888712245343</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4580.511221402512</v>
+        <v>4557.784007632579</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4447.191668260642</v>
+        <v>4426.494441269149</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4333.852925217973</v>
+        <v>4312.404901047059</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4222.827335969277</v>
+        <v>4200.164239142196</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4172.905873047005</v>
+        <v>4141.466917695649</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3978.108373047005</v>
+        <v>3866.982259974372</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.784095244165</v>
+        <v>3669.808246847323</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.305140906919</v>
+        <v>3567.337950533718</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.137530132589</v>
+        <v>3513.175636715236</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.681261596198</v>
+        <v>3485.721951228454</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.235857233998</v>
+        <v>3494.277538369915</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3507.048543689254</v>
+        <v>3507.090714148168</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.550239934912</v>
+        <v>3521.592091923671</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3534.022055754949</v>
+        <v>3534.063236278292</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.525492521406</v>
+        <v>3549.556234012565</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.298605322072</v>
+        <v>3452.290980457687</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.940884699431</v>
+        <v>3449.934178572648</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.047208038422</v>
+        <v>3450.041017263881</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3530.991964045421</v>
+        <v>3530.958945168903</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.323885686304</v>
+        <v>3626.260243936545</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.459684126276</v>
+        <v>3776.362668616905</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.114140830751</v>
+        <v>3848.026980057883</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.115192498743</v>
+        <v>3895.03261393417</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.0586117947</v>
+        <v>3880.986549657144</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.652812036139</v>
+        <v>3885.622052063209</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.204201250999</v>
+        <v>3993.193835565561</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.798892798948</v>
+        <v>4066.768823678052</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.493612983875</v>
+        <v>4106.456558427659</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.238681780989</v>
+        <v>4206.235378183464</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.868710244219</v>
+        <v>4198.854374958719</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.115803291013</v>
+        <v>4222.075244833315</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.891274427368</v>
+        <v>4242.849902100982</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.626021656817</v>
+        <v>4306.567547630688</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.218115781337</v>
+        <v>4398.143718004683</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4433.920226229937</v>
+        <v>4433.838771833032</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.119072949237</v>
+        <v>4534.009526075795</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4668.388278041461</v>
+        <v>4668.255430114377</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4748.071709007386</v>
+        <v>4747.897187605152</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.093164365931</v>
+        <v>4887.992554154376</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4928.707157765572</v>
+        <v>4928.596517588503</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5033.394530449043</v>
+        <v>5033.249233590421</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.671987920327</v>
+        <v>5204.587621088867</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.494968250243</v>
+        <v>5250.47622666413</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.976641586059</v>
+        <v>5297.057585566718</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5378.106483899388</v>
+        <v>5378.264786124102</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5457.540715924953</v>
+        <v>5457.746694503279</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5588.890669657181</v>
+        <v>5589.117208838441</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5532.497986711407</v>
+        <v>5532.791683492936</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5361.806151008663</v>
+        <v>5362.175016029995</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5244.149030561372</v>
+        <v>5244.499327450665</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5111.871808957761</v>
+        <v>5112.252904648323</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4996.005992345924</v>
+        <v>4996.353487747851</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4892.567063159153</v>
+        <v>4892.902798888086</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4846.531964588268</v>
+        <v>4846.911893344487</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4713.844076624035</v>
+        <v>4714.148609704247</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4587.278421253874</v>
+        <v>4587.488725883737</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4487.255894048839</v>
+        <v>4487.391952230174</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4482.574800185045</v>
+        <v>4482.713746166071</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4404.738683641927</v>
+        <v>4404.914098359096</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4250.295455838254</v>
+        <v>4250.534373715605</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4154.557158601238</v>
+        <v>4154.764674997115</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4100.917566614515</v>
+        <v>4101.055439315383</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4082.00305149928</v>
+        <v>4082.014243327615</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4122.125062874262</v>
+        <v>4121.94876779367</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4196.69884925541</v>
+        <v>4196.304932040781</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4290.521934357027</v>
+        <v>4289.986319829084</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4334.171962869224</v>
+        <v>4333.626711623257</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4341.840805965101</v>
+        <v>4341.366461974345</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4337.78269597301</v>
+        <v>4337.318111354121</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4343.044598574639</v>
+        <v>4342.70061205214</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4368.108370096882</v>
+        <v>4363.320070190577</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4418.956773844617</v>
+        <v>4412.190790213052</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4484.177394340879</v>
+        <v>4475.022927956983</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4544.264819024231</v>
+        <v>4533.095349409601</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4587.9656268239</v>
+        <v>4574.244292558938</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4628.50064578802</v>
+        <v>4612.547586242059</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4658.761984799687</v>
+        <v>4639.992939623013</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4625.888712245343</v>
+        <v>4605.47251282364</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4557.784007632579</v>
+        <v>4536.339190421602</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4426.494441269149</v>
+        <v>4407.366891606011</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4312.404901047059</v>
+        <v>4293.07063844591</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4200.164239142196</v>
+        <v>4180.575498690874</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4141.466917695649</v>
+        <v>4116.359341490778</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3866.982259974372</v>
+        <v>3871.177319773085</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.808246847323</v>
+        <v>3669.831982074745</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.337950533718</v>
+        <v>3567.370196130554</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.175636715236</v>
+        <v>3513.213089918368</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.721951228454</v>
+        <v>3485.761945511987</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.277538369915</v>
+        <v>3494.318507121472</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3507.090714148168</v>
+        <v>3507.132163764345</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.592091923671</v>
+        <v>3521.633228464709</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3534.063236278292</v>
+        <v>3534.103712831467</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.556234012565</v>
+        <v>3549.586456140946</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.290980457687</v>
+        <v>3452.283489028602</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.934178572648</v>
+        <v>3449.927590068018</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.041017263881</v>
+        <v>3450.034935257544</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3530.958945168903</v>
+        <v>3530.926501724296</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.260243936545</v>
+        <v>3626.197707681037</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.362668616905</v>
+        <v>3776.267329618029</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.026980057883</v>
+        <v>3847.94132175299</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.03261393417</v>
+        <v>3894.951442356706</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3880.986549657144</v>
+        <v>3880.915707234039</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.622052063209</v>
+        <v>3885.591803386233</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.193835565561</v>
+        <v>3993.183636716612</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.768823678052</v>
+        <v>4066.739264939548</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.456558427659</v>
+        <v>4106.42013372731</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.235378183464</v>
+        <v>4206.23214026741</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.854374958719</v>
+        <v>4198.840301406241</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.075244833315</v>
+        <v>4222.035409445896</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.849902100982</v>
+        <v>4242.809261506725</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.567547630688</v>
+        <v>4306.510101057733</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.143718004683</v>
+        <v>4398.070618596748</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4433.838771833032</v>
+        <v>4433.758728334153</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.009526075795</v>
+        <v>4533.901864295937</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4668.255430114377</v>
+        <v>4668.124871576018</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4747.897187605152</v>
+        <v>4747.725611432444</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4887.992554154376</v>
+        <v>4887.893672788792</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4928.596517588503</v>
+        <v>4928.487777689979</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5033.249233590421</v>
+        <v>5033.106419454647</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.587621088867</v>
+        <v>5204.504663207766</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.47622666413</v>
+        <v>5250.457715400797</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5297.057585566718</v>
+        <v>5297.137018593476</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5378.264786124102</v>
+        <v>5378.420277404945</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5457.746694503279</v>
+        <v>5457.949028130924</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5589.117208838441</v>
+        <v>5589.339756361902</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5532.791683492936</v>
+        <v>5533.080283423036</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5362.175016029995</v>
+        <v>5362.537521853687</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5244.499327450665</v>
+        <v>5244.843617868142</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5112.252904648323</v>
+        <v>5112.627517894245</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4996.353487747851</v>
+        <v>4996.695109693809</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4892.902798888086</v>
+        <v>4893.232906063535</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4846.911893344487</v>
+        <v>4847.285455708985</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4714.148609704247</v>
+        <v>4714.448027671884</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4587.488725883737</v>
+        <v>4587.695462626312</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4487.391952230174</v>
+        <v>4487.525638655959</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4482.713746166071</v>
+        <v>4482.850272895359</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4404.914098359096</v>
+        <v>4405.086492587374</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4250.534373715605</v>
+        <v>4250.769255042479</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4154.764674997115</v>
+        <v>4154.968811333549</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4101.055439315383</v>
+        <v>4101.191170175232</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4082.014243327615</v>
+        <v>4082.025552590521</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4121.94876779367</v>
+        <v>4121.775846154491</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4196.304932040781</v>
+        <v>4195.918003087849</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4289.986319829084</v>
+        <v>4289.459794871387</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4333.626711623257</v>
+        <v>4333.090077156155</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4341.366461974345</v>
+        <v>4340.899051046215</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4337.318111354121</v>
+        <v>4336.85981042587</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4342.70061205214</v>
+        <v>4342.36053657825</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4363.320070190577</v>
+        <v>4357.718067211347</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4412.190790213052</v>
+        <v>4404.594315117834</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4475.022927956983</v>
+        <v>4465.023082698113</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4533.095349409601</v>
+        <v>4520.981331153405</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4574.244292558938</v>
+        <v>4559.55453342996</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4612.547586242059</v>
+        <v>4595.607157357301</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4639.992939623013</v>
+        <v>4620.202155749073</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4605.47251282364</v>
+        <v>4583.919572419753</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4536.339190421602</v>
+        <v>4514.544917751758</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4407.366891606011</v>
+        <v>4386.201091367927</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4293.07063844591</v>
+        <v>4271.05151155594</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4180.575498690874</v>
+        <v>4157.297784143648</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4116.359341490778</v>
+        <v>4086.814719570325</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3871.177319773085</v>
+        <v>3853.85094813934</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.831982074745</v>
+        <v>3669.85531160168</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.370196130554</v>
+        <v>3567.401892117008</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.213089918368</v>
+        <v>3513.249906401797</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.761945511987</v>
+        <v>3485.801262116946</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.318507121472</v>
+        <v>3494.358781594054</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3507.132163764345</v>
+        <v>3507.17291086058</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.633228464709</v>
+        <v>3521.673667744956</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3534.103712831467</v>
+        <v>3534.143503309683</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.586456140946</v>
+        <v>3549.616171950869</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.283489028602</v>
+        <v>3452.276127563609</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.927590068018</v>
+        <v>3449.921116119068</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.034935257544</v>
+        <v>3450.028959179143</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3530.926501724296</v>
+        <v>3530.894618803246</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.197707681037</v>
+        <v>3626.136248372313</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.267329618029</v>
+        <v>3776.173624056888</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3847.94132175299</v>
+        <v>3847.857127406797</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3894.951442356706</v>
+        <v>3894.871642129764</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3880.915707234039</v>
+        <v>3880.846053841019</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.591803386233</v>
+        <v>3885.562053381471</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.183636716612</v>
+        <v>3993.17360072689</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.739264939548</v>
+        <v>4066.710203699785</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.42013372731</v>
+        <v>4106.384322962316</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.23214026741</v>
+        <v>4206.228966127052</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.840301406241</v>
+        <v>4198.826482509846</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.035409445896</v>
+        <v>4221.996277997544</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.809261506725</v>
+        <v>4242.769333436312</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.510101057733</v>
+        <v>4306.45365513682</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.070618596748</v>
+        <v>4397.998783915391</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4433.758728334153</v>
+        <v>4433.680059431814</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4533.901864295937</v>
+        <v>4533.796039409709</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4668.124871576018</v>
+        <v>4667.996543811638</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4747.725611432444</v>
+        <v>4747.556906629269</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4887.893672788792</v>
+        <v>4887.796476135899</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4928.487777689979</v>
+        <v>4928.380889583166</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5033.106419454647</v>
+        <v>5032.966025040327</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.504663207766</v>
+        <v>5204.423079347755</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.457715400797</v>
+        <v>5250.439430935792</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5297.137018593476</v>
+        <v>5297.214982310182</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5378.420277404945</v>
+        <v>5378.573031824495</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5457.949028130924</v>
+        <v>5458.147812534988</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5589.339756361902</v>
+        <v>5589.558416652855</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5533.080283423036</v>
+        <v>5533.363917905876</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5362.537521853687</v>
+        <v>5362.893831306472</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5244.843617868142</v>
+        <v>5245.182054770312</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5112.627517894245</v>
+        <v>5112.995812439629</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4996.695109693809</v>
+        <v>4997.031005645122</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4893.232906063535</v>
+        <v>4893.557524816126</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4847.285455708985</v>
+        <v>4847.652810085838</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4714.448027671884</v>
+        <v>4714.742458129005</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4587.695462626312</v>
+        <v>4587.898721407812</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4487.525638655959</v>
+        <v>4487.657014710695</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4482.850272895359</v>
+        <v>4482.984442929926</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4405.086492587374</v>
+        <v>4405.255943557495</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4250.769255042479</v>
+        <v>4251.000200975886</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4154.968811333549</v>
+        <v>4155.169649013269</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4101.191170175232</v>
+        <v>4101.324808053964</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4082.025552590521</v>
+        <v>4082.036968706479</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4121.775846154491</v>
+        <v>4121.606204171241</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4195.918003087849</v>
+        <v>4195.53788065944</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4289.459794871387</v>
+        <v>4288.9421337157</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4333.090077156155</v>
+        <v>4332.561862408389</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4340.899051046215</v>
+        <v>4340.438430332494</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4336.85981042587</v>
+        <v>4336.407677656536</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4342.36053657825</v>
+        <v>4342.024321625443</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4357.718067211347</v>
+        <v>4352.33696312577</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4404.594315117834</v>
+        <v>4397.296101143691</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4465.023082698113</v>
+        <v>4455.41788212038</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4520.981331153405</v>
+        <v>4509.37080062259</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4559.55453342996</v>
+        <v>4545.48864831292</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4595.607157357301</v>
+        <v>4579.415357316996</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4620.202155749073</v>
+        <v>4601.356633535192</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4583.919572419753</v>
+        <v>4563.504292985879</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4514.544917751758</v>
+        <v>4494.076513416747</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4386.201091367927</v>
+        <v>4366.542839831997</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4271.05151155594</v>
+        <v>4251.024522047332</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4157.297784143648</v>
+        <v>4136.818464167842</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4086.814719570325</v>
+        <v>4062.243997492033</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3853.85094813934</v>
+        <v>3842.311273777468</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.85531160168</v>
+        <v>3669.878245741546</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.401892117008</v>
+        <v>3567.433052425322</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.249906401797</v>
+        <v>3513.286102263784</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.801262116946</v>
+        <v>3485.839918119905</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.358781594054</v>
+        <v>3494.398379284767</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3507.17291086058</v>
+        <v>3507.212973144007</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.673667744956</v>
+        <v>3521.713427340199</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3534.143503309683</v>
+        <v>3534.182625006804</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.616171950869</v>
+        <v>3549.645394053688</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.276127563609</v>
+        <v>3452.26889271083</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.921116119068</v>
+        <v>3449.91475376496</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.028959179143</v>
+        <v>3450.023086286407</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3530.894618803246</v>
+        <v>3530.863282007851</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.136248372313</v>
+        <v>3626.07583843713</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.173624056888</v>
+        <v>3776.081510323284</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3847.857127406797</v>
+        <v>3847.774359814633</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3894.871642129764</v>
+        <v>3894.793178809548</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3880.846053841019</v>
+        <v>3880.777559813621</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.562053381471</v>
+        <v>3885.532789836694</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.17360072689</v>
+        <v>3993.163723743902</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.710203699785</v>
+        <v>4066.681627505078</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.384322962316</v>
+        <v>4106.349110744111</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.228966127052</v>
+        <v>4206.22585392866</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.826482509846</v>
+        <v>4198.812911444614</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4221.996277997544</v>
+        <v>4221.95783202495</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.769333436312</v>
+        <v>4242.73009934681</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.45365513682</v>
+        <v>4306.398183989515</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4397.998783915391</v>
+        <v>4397.928181469068</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4433.680059431814</v>
+        <v>4433.602730057907</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4533.796039409709</v>
+        <v>4533.692004845063</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4667.996543811638</v>
+        <v>4667.870390188511</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4747.556906629269</v>
+        <v>4747.391001782416</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4887.796476135899</v>
+        <v>4887.700921550274</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4928.380889583166</v>
+        <v>4928.27580641511</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5032.966025040327</v>
+        <v>5032.827989456671</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.423079347755</v>
+        <v>5204.342835722166</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.439430935792</v>
+        <v>5250.421369783482</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5297.214982310182</v>
+        <v>5297.291516852692</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5378.573031824495</v>
+        <v>5378.723120888917</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5458.147812534988</v>
+        <v>5458.343140125264</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5589.558416652855</v>
+        <v>5589.77329053065</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5533.363917905876</v>
+        <v>5533.642713871428</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5362.893831306472</v>
+        <v>5363.244101710419</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5245.182054770312</v>
+        <v>5245.514785971238</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5112.995812439629</v>
+        <v>5113.357946568538</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4997.031005645122</v>
+        <v>4997.361318174595</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4893.557524816126</v>
+        <v>4893.876790671056</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4847.652810085838</v>
+        <v>4848.014109676962</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4714.742458129005</v>
+        <v>4715.032024475139</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4587.898721407812</v>
+        <v>4588.098589161126</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4487.657014710695</v>
+        <v>4487.786139681872</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4482.984442929926</v>
+        <v>4483.116316691121</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4405.255943557495</v>
+        <v>4405.422525893453</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4251.000200975886</v>
+        <v>4251.227309330331</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4155.169649013269</v>
+        <v>4155.367266863534</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4101.324808053964</v>
+        <v>4101.456400360217</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4082.036968706479</v>
+        <v>4082.048481694553</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4121.606204171241</v>
+        <v>4121.439751440559</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4195.53788065944</v>
+        <v>4195.164389183579</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4288.9421337157</v>
+        <v>4288.433117888341</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4332.561862408389</v>
+        <v>4332.041876087222</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4340.438430332494</v>
+        <v>4339.984460580595</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4336.407677656536</v>
+        <v>4335.961599891006</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4342.024321625443</v>
+        <v>4341.691916811242</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4352.33696312577</v>
+        <v>4352.18773842718</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4397.296101143691</v>
+        <v>4391.724419962587</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4455.41788212038</v>
+        <v>4447.830240771756</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4509.37080062259</v>
+        <v>4499.392785242421</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4545.48864831292</v>
+        <v>4532.868208318232</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4579.415357316996</v>
+        <v>4565.637383949728</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4601.356633535192</v>
+        <v>4586.152192945145</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4563.504292985879</v>
+        <v>4548.071462934833</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4494.076513416747</v>
+        <v>4479.094568643709</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4366.542839831997</v>
+        <v>4353.903061284729</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4251.024522047332</v>
+        <v>4240.942104105839</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4136.818464167842</v>
+        <v>4131.336931113499</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4062.243997492033</v>
+        <v>4060.254748551906</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,15 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3842.311273777468</v>
+        <v>3870.142553935244</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
+        <v>46395</v>
+      </c>
+      <c r="B85">
+        <v>4018.828966990278</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4447.830240771756</v>
+        <v>4447.986681119753</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4499.392785242421</v>
+        <v>4499.483737515951</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4532.868208318232</v>
+        <v>4533.491015283764</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4565.637383949728</v>
+        <v>4566.188755809016</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4586.152192945145</v>
+        <v>4586.570085399276</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4548.071462934833</v>
+        <v>4548.394286924444</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4479.094568643709</v>
+        <v>4479.350378641365</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4353.903061284729</v>
+        <v>4354.11275956146</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4240.942104105839</v>
+        <v>4241.658934997341</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4131.336931113499</v>
+        <v>4131.467256574742</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4060.254748551906</v>
+        <v>4060.376048036738</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3870.142553935244</v>
+        <v>3870.292640915677</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>4018.828966990278</v>
+        <v>4019.528335096429</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.878245741546</v>
+        <v>3669.900794461133</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.433052425322</v>
+        <v>3567.463690520806</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.286102263784</v>
+        <v>3513.321693064485</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.839918119905</v>
+        <v>3485.877930028571</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.398379284767</v>
+        <v>3494.437317107776</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3507.212973144007</v>
+        <v>3507.252367731734</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.713427340199</v>
+        <v>3521.752524240543</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3534.182625006804</v>
+        <v>3534.221094640407</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.645394053688</v>
+        <v>3549.674134645601</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.26889271083</v>
+        <v>3452.261781232633</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.91475376496</v>
+        <v>3449.908500145985</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.023086286407</v>
+        <v>3450.017313930869</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3530.863282007851</v>
+        <v>3530.832477429005</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.07583843713</v>
+        <v>3626.016451235279</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.081510323284</v>
+        <v>3775.990948208038</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3847.774359814633</v>
+        <v>3847.692983021681</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3894.793178809548</v>
+        <v>3894.716019095592</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3880.777559813621</v>
+        <v>3880.710196465293</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.532789836694</v>
+        <v>3885.504000934574</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.163723743902</v>
+        <v>3993.154002035104</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.681627505078</v>
+        <v>4066.653524313918</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.349110744111</v>
+        <v>4106.314482194051</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.22585392866</v>
+        <v>4206.222801907204</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.812911444614</v>
+        <v>4198.799581626567</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4221.95783202495</v>
+        <v>4221.920053703853</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.73009934681</v>
+        <v>4242.691541332128</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.398183989515</v>
+        <v>4306.34366262076</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4397.928181469068</v>
+        <v>4397.858779868149</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4433.602730057907</v>
+        <v>4433.526706325832</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4533.692004845063</v>
+        <v>4533.589715589769</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4667.870390188511</v>
+        <v>4667.74635597294</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4747.391001782416</v>
+        <v>4747.22782782506</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4887.700921550274</v>
+        <v>4887.606967812237</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4928.27580641511</v>
+        <v>4928.172482898563</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5032.827989456671</v>
+        <v>5032.692253835975</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.342835722166</v>
+        <v>5204.263899640704</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.421369783482</v>
+        <v>5250.403528498806</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5297.291516852692</v>
+        <v>5297.366660916203</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5378.723120888917</v>
+        <v>5378.870613638856</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5458.343140125264</v>
+        <v>5458.535100136482</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5589.77329053065</v>
+        <v>5589.984475362802</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5533.642713871428</v>
+        <v>5533.916793964105</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5363.244101710419</v>
+        <v>5363.588485113311</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5245.514785971238</v>
+        <v>5245.841954356534</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5113.357946568538</v>
+        <v>5113.714073330336</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4997.361318174595</v>
+        <v>4997.686185167134</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4893.876790671056</v>
+        <v>4894.190834735417</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4848.014109676962</v>
+        <v>4848.36950269352</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4715.032024475139</v>
+        <v>4715.316846078604</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4588.098589161126</v>
+        <v>4588.295149949188</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4487.786139681872</v>
+        <v>4487.913070848629</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4483.116316691121</v>
+        <v>4483.245952554877</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4405.422525893453</v>
+        <v>4405.586311721387</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4251.227309330331</v>
+        <v>4251.45067471434</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4155.367266863534</v>
+        <v>4155.561741236424</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4101.456400360217</v>
+        <v>4101.585993103803</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4082.048481694553</v>
+        <v>4082.060082139661</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4121.439751440559</v>
+        <v>4121.276400792432</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4195.164389183579</v>
+        <v>4194.79735899755</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4288.433117888341</v>
+        <v>4287.932535922975</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4332.041876087222</v>
+        <v>4331.529932466075</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4339.984460580595</v>
+        <v>4339.537006035937</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4335.961599891006</v>
+        <v>4335.521466313405</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4341.691916811242</v>
+        <v>4341.363271951228</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4352.18773842718</v>
+        <v>4352.03893263502</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4391.724419962587</v>
+        <v>4385.443084147451</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4447.986681119753</v>
+        <v>4439.729845543233</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4499.483737515951</v>
+        <v>4488.732883911044</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4533.491015283764</v>
+        <v>4520.4715272091</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4566.188755809016</v>
+        <v>4551.735297285053</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4586.570085399276</v>
+        <v>4570.388403149841</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4548.394286924444</v>
+        <v>4531.639019307626</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4479.350378641365</v>
+        <v>4462.637712862106</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4354.11275956146</v>
+        <v>4339.130604371042</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4241.658934997341</v>
+        <v>4229.217510111866</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4131.467256574742</v>
+        <v>4121.64158189406</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4060.376048036738</v>
+        <v>4051.886015798017</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3870.292640915677</v>
+        <v>3879.218910292187</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>4019.528335096429</v>
+        <v>3971.47237649905</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.900794461133</v>
+        <v>3669.683097984353</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.463690520806</v>
+        <v>3567.167955415172</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.321693064485</v>
+        <v>3512.978215735504</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.877930028571</v>
+        <v>3485.511173905877</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.437317107776</v>
+        <v>3494.061623916291</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3507.252367731734</v>
+        <v>3506.872263870171</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.752524240543</v>
+        <v>3521.37529083346</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3534.221094640407</v>
+        <v>3533.849913492854</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.674134645601</v>
+        <v>3549.397055812055</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.261781232633</v>
+        <v>3452.330513041597</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.908500145985</v>
+        <v>3449.968950728269</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.017313930869</v>
+        <v>3450.073119307995</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3530.832477429005</v>
+        <v>3531.130111216435</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.016451235279</v>
+        <v>3626.590115172073</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3775.990948208038</v>
+        <v>3776.865427641812</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3847.692983021681</v>
+        <v>3848.478627767185</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3894.716019095592</v>
+        <v>3895.460334100945</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3880.710196465293</v>
+        <v>3881.359709413277</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.504000934574</v>
+        <v>3885.781232767598</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.154002035104</v>
+        <v>3993.247416560236</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.653524313918</v>
+        <v>4066.924546904342</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.314482194051</v>
+        <v>4106.648468128793</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.222801907204</v>
+        <v>4206.252593826347</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.799581626567</v>
+        <v>4198.928819750338</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4221.920053703853</v>
+        <v>4222.285675576759</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.691541332128</v>
+        <v>4243.064490237538</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.34366262076</v>
+        <v>4306.870762993799</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4397.858779868149</v>
+        <v>4398.52940664132</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4433.526706325832</v>
+        <v>4434.260925139321</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4533.589715589769</v>
+        <v>4534.57713647804</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4667.74635597294</v>
+        <v>4668.943810328462</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4747.22782782506</v>
+        <v>4748.800815817993</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4887.606967812237</v>
+        <v>4888.513832172483</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4928.172482898563</v>
+        <v>4929.16975230913</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5032.692253835975</v>
+        <v>5034.001884306603</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.263899640704</v>
+        <v>5205.0242861181</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.403528498806</v>
+        <v>5250.57230954739</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5297.366660916203</v>
+        <v>5296.636866370256</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5378.870613638856</v>
+        <v>5377.443587007721</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5458.535100136482</v>
+        <v>5456.678312827651</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5589.984475362802</v>
+        <v>5587.942372292044</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5533.916793964105</v>
+        <v>5531.269434960384</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5363.588485113311</v>
+        <v>5360.263635798987</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5245.841954356534</v>
+        <v>5242.684526216466</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5113.714073330336</v>
+        <v>5110.279122136287</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4997.686185167134</v>
+        <v>4994.554143724038</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4894.190834735417</v>
+        <v>4891.164859588916</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4848.36950269352</v>
+        <v>4844.945222717744</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4715.316846078604</v>
+        <v>4712.572083695402</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4588.295149949188</v>
+        <v>4586.399613109158</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4487.913070848629</v>
+        <v>4486.686637309354</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4483.245952554877</v>
+        <v>4481.993492384731</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4405.586311721387</v>
+        <v>4404.005177440446</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4251.45067471434</v>
+        <v>4249.297270445926</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4155.561741236424</v>
+        <v>4164.621216894048</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4101.585993103803</v>
+        <v>4103.308654881091</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4082.060082139661</v>
+        <v>4078.031407234403</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4121.276400792432</v>
+        <v>4095.891780147499</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4194.79735899755</v>
+        <v>4151.227856197243</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4287.932535922975</v>
+        <v>4230.953105282369</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4331.529932466075</v>
+        <v>4271.150881641332</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4339.537006035937</v>
+        <v>4297.451682647637</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4335.521466313405</v>
+        <v>4306.012535741813</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4341.363271951228</v>
+        <v>4326.156532024605</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4352.03893263502</v>
+        <v>4351.1548161461</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4385.443084147451</v>
+        <v>4376.308503288405</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4439.729845543233</v>
+        <v>4408.908361405751</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4488.732883911044</v>
+        <v>4468.891280354469</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4520.4715272091</v>
+        <v>4488.704009874387</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4551.735297285053</v>
+        <v>4533.888890012485</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4570.388403149841</v>
+        <v>4561.052991512604</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4531.639019307626</v>
+        <v>4537.100480496536</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4462.637712862106</v>
+        <v>4451.466680414485</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4339.130604371042</v>
+        <v>4307.239108922849</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4229.217510111866</v>
+        <v>4183.658440522888</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4121.64158189406</v>
+        <v>4058.210454216655</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4051.886015798017</v>
+        <v>3932.620681101272</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3879.218910292187</v>
+        <v>3723.366537709982</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>3971.47237649905</v>
+        <v>3964.969995511876</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.683097984353</v>
+        <v>3669.944773859424</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.167955415172</v>
+        <v>3567.523451715343</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3512.978215735504</v>
+        <v>3513.391119164867</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.511173905877</v>
+        <v>3485.952084889329</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.061623916291</v>
+        <v>3494.513278035849</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.872263870171</v>
+        <v>3507.329219483438</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.37529083346</v>
+        <v>3521.828795132458</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.849913492854</v>
+        <v>3534.296141847523</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.397055812055</v>
+        <v>3549.730218106494</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.330513041597</v>
+        <v>3452.247915991984</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.968950728269</v>
+        <v>3449.896308154771</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.073119307995</v>
+        <v>3450.006060682911</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.130111216435</v>
+        <v>3530.77241160616</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.590115172073</v>
+        <v>3625.900642903117</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.865427641812</v>
+        <v>3775.814324653169</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.478627767185</v>
+        <v>3847.534263953718</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.460334100945</v>
+        <v>3894.565482721361</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.359709413277</v>
+        <v>3880.578751711523</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.781232767598</v>
+        <v>3885.447801669451</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.247416560236</v>
+        <v>3993.135010082202</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.924546904342</v>
+        <v>4066.598690736462</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.648468128793</v>
+        <v>4106.246919008752</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.252593826347</v>
+        <v>4206.216871659764</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.928819750338</v>
+        <v>4198.773620538308</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.285675576759</v>
+        <v>4221.846431751522</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.064490237538</v>
+        <v>4242.616384926019</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.870762993799</v>
+        <v>4306.237373433529</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.52940664132</v>
+        <v>4397.723458878279</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.260925139321</v>
+        <v>4433.378445854962</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.57713647804</v>
+        <v>4533.39020037236</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4668.943810328462</v>
+        <v>4667.50443585553</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4748.800815817993</v>
+        <v>4746.909407475209</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.513832172483</v>
+        <v>4887.423704777675</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4929.16975230913</v>
+        <v>4927.970941113976</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5034.001884306603</v>
+        <v>5032.427456632878</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5205.0242861181</v>
+        <v>5204.109824568804</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.57230954739</v>
+        <v>5250.368491963687</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.636866370256</v>
+        <v>5297.51292556286</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5377.443587007721</v>
+        <v>5379.158074656026</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5456.678312827651</v>
+        <v>5458.909259288408</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5587.942372292044</v>
+        <v>5590.396150971415</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5531.269434960384</v>
+        <v>5534.451276746942</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5360.263635798987</v>
+        <v>5364.260174038327</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5242.684526216466</v>
+        <v>5246.480150791096</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5110.279122136287</v>
+        <v>5114.408892051837</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4994.554143724038</v>
+        <v>4998.320111777388</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4891.164859588916</v>
+        <v>4894.803760891344</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4844.945222717744</v>
+        <v>4849.063138091434</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4712.572083695402</v>
+        <v>4715.872713344997</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4586.399613109158</v>
+        <v>4588.678673229794</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4486.686637309354</v>
+        <v>4488.160571344714</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4481.993492384731</v>
+        <v>4483.498734376799</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4404.005177440446</v>
+        <v>4405.905770484384</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4249.297270445926</v>
+        <v>4251.886539748471</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4164.621216894048</v>
+        <v>4155.941553152341</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4103.308654881091</v>
+        <v>4101.839357247345</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4078.031407234403</v>
+        <v>4082.083510376699</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4095.891780147499</v>
+        <v>4120.958672391242</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4151.227856197243</v>
+        <v>4194.082031941435</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4230.953105282369</v>
+        <v>4286.955861117987</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4271.150881641332</v>
+        <v>4330.529457099032</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4297.451682647637</v>
+        <v>4338.661116469915</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4306.012535741813</v>
+        <v>4334.658599923427</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4326.156532024605</v>
+        <v>4340.717062628519</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4351.1548161461</v>
+        <v>4351.742723613112</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4376.308503288405</v>
+        <v>4376.244791709845</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4408.908361405751</v>
+        <v>4427.467467541246</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4468.891280354469</v>
+        <v>4472.171864195156</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4488.704009874387</v>
+        <v>4500.20593175974</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4533.888890012485</v>
+        <v>4529.92862072478</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4561.052991512604</v>
+        <v>4546.313373212379</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4537.100480496536</v>
+        <v>4507.673820495693</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4451.466680414485</v>
+        <v>4440.221427716663</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4307.239108922849</v>
+        <v>4321.774082300077</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4183.658440522888</v>
+        <v>4217.963905543355</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4058.210454216655</v>
+        <v>4118.556181702143</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>3932.620681101272</v>
+        <v>4056.196350492205</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3723.366537709982</v>
+        <v>3920.548036694937</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>3964.969995511876</v>
+        <v>4019.559470602183</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.944773859424</v>
+        <v>3669.709029658157</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.523451715343</v>
+        <v>3567.203175881357</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.391119164867</v>
+        <v>3513.019114558123</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.952084889329</v>
+        <v>3485.554834445998</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.513278035849</v>
+        <v>3494.106348772337</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3507.329219483438</v>
+        <v>3506.917514216417</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.828795132458</v>
+        <v>3521.420199673311</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3534.296141847523</v>
+        <v>3533.894101828321</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.730218106494</v>
+        <v>3549.430014533355</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.247915991984</v>
+        <v>3452.32231714361</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.896308154771</v>
+        <v>3449.961741163574</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.006060682911</v>
+        <v>3450.06646293833</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3530.77241160616</v>
+        <v>3531.094630494626</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3625.900642903117</v>
+        <v>3626.52174491703</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3775.814324653169</v>
+        <v>3776.761243768845</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3847.534263953718</v>
+        <v>3848.385043852333</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3894.565482721361</v>
+        <v>3895.371745485412</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3880.578751711523</v>
+        <v>3881.282439580379</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.447801669451</v>
+        <v>3885.74829251343</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.135010082202</v>
+        <v>3993.236341078434</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.598690736462</v>
+        <v>4066.892298141928</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.246919008752</v>
+        <v>4106.608723467499</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.216871659764</v>
+        <v>4206.249006876353</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.773620538308</v>
+        <v>4198.913361299088</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4221.846431751522</v>
+        <v>4222.242019067084</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.616384926019</v>
+        <v>4243.019984505348</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.237373433529</v>
+        <v>4306.807891191727</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4397.723458878279</v>
+        <v>4398.449454101158</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4433.378445854962</v>
+        <v>4434.173437492573</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4533.39020037236</v>
+        <v>4534.459532081635</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4667.50443585553</v>
+        <v>4668.801175900584</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4746.909407475209</v>
+        <v>4748.613722148875</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4887.423704777675</v>
+        <v>4888.405833124471</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4927.970941113976</v>
+        <v>4929.050990878526</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5032.427456632878</v>
+        <v>5033.845981003215</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.109824568804</v>
+        <v>5204.933909586498</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.368491963687</v>
+        <v>5250.552610727176</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5297.51292556286</v>
+        <v>5296.724303340468</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5379.158074656026</v>
+        <v>5377.613929590347</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5458.909259288408</v>
+        <v>5456.899900249002</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5590.396150971415</v>
+        <v>5588.186000351059</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5534.451276746942</v>
+        <v>5531.584929855951</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5364.260174038327</v>
+        <v>5360.65968473714</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5246.480150791096</v>
+        <v>5243.06048954636</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5114.408892051837</v>
+        <v>5110.687902810678</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4998.320111777388</v>
+        <v>4994.926712954491</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4894.803760891344</v>
+        <v>4891.524610056659</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4849.063138091434</v>
+        <v>4845.352313148409</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4715.872713344997</v>
+        <v>4712.898443801059</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4588.678673229794</v>
+        <v>4586.625153105038</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4488.160571344714</v>
+        <v>4486.832841674632</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4483.498734376799</v>
+        <v>4482.142787093614</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4405.905770484384</v>
+        <v>4404.193502698236</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4251.886539748471</v>
+        <v>4249.553418128741</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4155.941553152341</v>
+        <v>4164.843100465159</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4101.839357247345</v>
+        <v>4103.456355511777</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4082.083510376699</v>
+        <v>4078.060167983114</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4120.958672391242</v>
+        <v>4095.766871180607</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4194.082031941435</v>
+        <v>4150.895727161444</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4286.955861117987</v>
+        <v>4230.456291812308</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4330.529457099032</v>
+        <v>4270.606125685848</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4338.661116469915</v>
+        <v>4296.930947350936</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4334.658599923427</v>
+        <v>4305.491665893389</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4340.717062628519</v>
+        <v>4325.736471523443</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4351.742723613112</v>
+        <v>4350.915033457835</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4376.244791709845</v>
+        <v>4371.634693287746</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4427.467467541246</v>
+        <v>4403.50572033844</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4472.171864195156</v>
+        <v>4461.491204685666</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4500.20593175974</v>
+        <v>4480.16910004463</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4529.92862072478</v>
+        <v>4525.159230799828</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4546.313373212379</v>
+        <v>4550.674968341073</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4507.673820495693</v>
+        <v>4526.660853649806</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4440.221427716663</v>
+        <v>4442.280352133682</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4321.774082300077</v>
+        <v>4301.40922909485</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4217.963905543355</v>
+        <v>4181.353464928248</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4118.556181702143</v>
+        <v>4061.36993743788</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4056.196350492205</v>
+        <v>3944.762178725651</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3920.548036694937</v>
+        <v>3761.812629487491</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>4019.559470602183</v>
+        <v>3985.364089050183</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.709029658157</v>
+        <v>3669.966222864995</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.203175881357</v>
+        <v>3567.552599580233</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.019114558123</v>
+        <v>3513.424983089602</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.554834445998</v>
+        <v>3485.988258218211</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.106348772337</v>
+        <v>3494.550332265312</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.917514216417</v>
+        <v>3507.366708144918</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.420199673311</v>
+        <v>3521.866000387637</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.894101828321</v>
+        <v>3534.332750183156</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.430014533355</v>
+        <v>3549.757583440424</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.32231714361</v>
+        <v>3452.241156283278</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.961741163574</v>
+        <v>3449.890364531298</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.06646293833</v>
+        <v>3450.000574927808</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.094630494626</v>
+        <v>3530.743124807947</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.52174491703</v>
+        <v>3625.844172815092</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.761243768845</v>
+        <v>3775.728189288517</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.385043852333</v>
+        <v>3847.456855562698</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.371745485412</v>
+        <v>3894.492044764934</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.282439580379</v>
+        <v>3880.514617472696</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.74829251343</v>
+        <v>3885.420369507775</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.236341078434</v>
+        <v>3993.125732932323</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.892298141928</v>
+        <v>4066.571938179926</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.608723467499</v>
+        <v>4106.213956982397</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.249006876353</v>
+        <v>4206.213990219706</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.913361299088</v>
+        <v>4198.760977212942</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.242019067084</v>
+        <v>4221.810555427563</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4243.019984505348</v>
+        <v>4242.579753669771</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.807891191727</v>
+        <v>4306.185559715217</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.449454101158</v>
+        <v>4397.657481814703</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.173437492573</v>
+        <v>4433.306146818933</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.459532081635</v>
+        <v>4533.292891618298</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4668.801175900584</v>
+        <v>4667.386449290929</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4748.613722148875</v>
+        <v>4746.754033844474</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.405833124471</v>
+        <v>4887.334319653639</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4929.050990878526</v>
+        <v>4927.872639532599</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5033.845981003215</v>
+        <v>5032.298286701729</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.933909586498</v>
+        <v>5204.034625293858</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.552610727176</v>
+        <v>5250.351290038284</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.724303340468</v>
+        <v>5297.584116890381</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5377.613929590347</v>
+        <v>5379.298169597295</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5456.899900249002</v>
+        <v>5459.091622204403</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5588.186000351059</v>
+        <v>5590.596820503886</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5531.584929855951</v>
+        <v>5534.711904866805</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5360.65968473714</v>
+        <v>5364.587759201427</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5243.06048954636</v>
+        <v>5246.791441750894</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5110.687902810678</v>
+        <v>5114.747865813801</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4994.926712954491</v>
+        <v>4998.629425397357</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4891.524610056659</v>
+        <v>4895.102884668733</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4845.352313148409</v>
+        <v>4849.401653704559</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4712.898443801059</v>
+        <v>4716.143979016935</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4586.625153105038</v>
+        <v>4588.865790526193</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4486.832841674632</v>
+        <v>4488.281245927677</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4482.142787093614</v>
+        <v>4483.621987610166</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4404.193502698236</v>
+        <v>4406.061576088734</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4249.553418128741</v>
+        <v>4252.099213724054</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4164.843100465159</v>
+        <v>4156.127031863258</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4103.456355511777</v>
+        <v>4101.96321411446</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4078.060167983114</v>
+        <v>4082.095321884826</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4095.766871180607</v>
+        <v>4120.804135230813</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4150.895727161444</v>
+        <v>4193.733423159362</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4230.456291812308</v>
+        <v>4286.479377978223</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4270.606125685848</v>
+        <v>4330.040580032821</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4296.930947350936</v>
+        <v>4338.232426582086</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4305.491665893389</v>
+        <v>4334.235656825784</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4325.736471523443</v>
+        <v>4340.39939919415</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4350.915033457835</v>
+        <v>4351.595386953117</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4371.634693287746</v>
+        <v>4372.174827853682</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4403.50572033844</v>
+        <v>4422.06500450678</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4461.491204685666</v>
+        <v>4464.767788860378</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4480.16910004463</v>
+        <v>4491.068058328159</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4525.159230799828</v>
+        <v>4520.300964789734</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4550.674968341073</v>
+        <v>4535.77769439758</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4526.660853649806</v>
+        <v>4497.384989975872</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4442.280352133682</v>
+        <v>4430.890462157882</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4301.40922909485</v>
+        <v>4315.051487497015</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4181.353464928248</v>
+        <v>4214.493807751888</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4061.36993743788</v>
+        <v>4118.607196553401</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>3944.762178725651</v>
+        <v>4059.756752886728</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3761.812629487491</v>
+        <v>3938.309972883509</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>3985.364089050183</v>
+        <v>4035.264884899253</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4422.06500450678</v>
+        <v>4422.200303396851</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4464.767788860378</v>
+        <v>4464.82705810404</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4491.068058328159</v>
+        <v>4491.588896616501</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4520.300964789734</v>
+        <v>4520.397450655139</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4535.77769439758</v>
+        <v>4535.879384313843</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4497.384989975872</v>
+        <v>4497.498778089212</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4430.890462157882</v>
+        <v>4431.021793630564</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4315.051487497015</v>
+        <v>4315.204170870225</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4214.493807751888</v>
+        <v>4214.70711669477</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4118.607196553401</v>
+        <v>4118.619766086411</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4059.756752886728</v>
+        <v>4059.767706027152</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3938.309972883509</v>
+        <v>3938.321274756924</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>4035.264884899253</v>
+        <v>4035.281472329891</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.966222864995</v>
+        <v>3669.734498303606</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.552599580233</v>
+        <v>3567.237769318303</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.424983089602</v>
+        <v>3513.059287232209</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.988258218211</v>
+        <v>3485.597722479602</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.550332265312</v>
+        <v>3494.150282184822</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3507.366708144918</v>
+        <v>3506.961963710389</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.866000387637</v>
+        <v>3521.464313648664</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3534.332750183156</v>
+        <v>3533.93750805068</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.757583440424</v>
+        <v>3549.462396995295</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.241156283278</v>
+        <v>3452.314269870662</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.890364531298</v>
+        <v>3449.954662642295</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.000574927808</v>
+        <v>3450.059927769912</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3530.743124807947</v>
+        <v>3531.059790417996</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3625.844172815092</v>
+        <v>3626.454604992303</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3775.728189288517</v>
+        <v>3776.658924672649</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3847.456855562698</v>
+        <v>3848.29313068979</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3894.492044764934</v>
+        <v>3895.284719414598</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3880.514617472696</v>
+        <v>3881.206523317541</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.420369507775</v>
+        <v>3885.71591852796</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.125732932323</v>
+        <v>3993.225449694854</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.571938179926</v>
+        <v>4066.860615985612</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.213956982397</v>
+        <v>4106.569678146007</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.213990219706</v>
+        <v>4206.245494025145</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.760977212942</v>
+        <v>4198.898195653069</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4221.810555427563</v>
+        <v>4222.199169465788</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.579753669771</v>
+        <v>4242.976294618451</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.185559715217</v>
+        <v>4306.74616413737</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4397.657481814703</v>
+        <v>4398.370947073035</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4433.306146818933</v>
+        <v>4434.087519421469</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4533.292891618298</v>
+        <v>4534.344023350177</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4667.386449290929</v>
+        <v>4668.661086959784</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4746.754033844474</v>
+        <v>4748.429895813269</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4887.334319653639</v>
+        <v>4888.29975569507</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4927.872639532599</v>
+        <v>4928.934341506471</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5032.298286701729</v>
+        <v>5033.692835450824</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.034625293858</v>
+        <v>5204.845094158414</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.351290038284</v>
+        <v>5250.533156670208</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5297.584116890381</v>
+        <v>5296.810046216997</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5379.298169597295</v>
+        <v>5377.781136698324</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5459.091622204403</v>
+        <v>5457.117423513592</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5590.596820503886</v>
+        <v>5588.425179606968</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5534.711904866805</v>
+        <v>5531.894753403658</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5364.587759201427</v>
+        <v>5361.048663074727</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5246.791441750894</v>
+        <v>5243.429778465638</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5114.747865813801</v>
+        <v>5111.089486531355</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4998.629425397357</v>
+        <v>4995.292765609234</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4895.102884668733</v>
+        <v>4891.878121299497</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4849.401653704559</v>
+        <v>4845.752346928734</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4716.143979016935</v>
+        <v>4713.219132614947</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4588.865790526193</v>
+        <v>4586.846732875287</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4488.281245927677</v>
+        <v>4486.976405831083</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4483.621987610166</v>
+        <v>4482.289388985795</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4406.061576088734</v>
+        <v>4404.378470090369</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4252.099213724054</v>
+        <v>4249.805088222853</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4156.127031863258</v>
+        <v>4165.061214434967</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4101.96321411446</v>
+        <v>4103.601679109728</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4082.095321884826</v>
+        <v>4078.088748912716</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4120.804135230813</v>
+        <v>4095.644575417714</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4193.733423159362</v>
+        <v>4150.569858559531</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4286.479377978223</v>
+        <v>4229.968484682555</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4330.040580032821</v>
+        <v>4270.070752102073</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4338.232426582086</v>
+        <v>4296.418709476651</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4334.235656825784</v>
+        <v>4304.978703083914</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4340.39939919415</v>
+        <v>4325.322113731112</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4351.595386953117</v>
+        <v>4350.677368011213</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4372.174827853682</v>
+        <v>4371.617337019001</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4422.200303396851</v>
+        <v>4398.037458644558</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4464.82705810404</v>
+        <v>4453.839117886395</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4491.588896616501</v>
+        <v>4472.504172923578</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4520.397450655139</v>
+        <v>4515.517114978314</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4535.879384313843</v>
+        <v>4538.677310151307</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4497.498778089212</v>
+        <v>4515.44220897185</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4431.021793630564</v>
+        <v>4431.71678709173</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4315.204170870225</v>
+        <v>4293.155493237056</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4214.70711669477</v>
+        <v>4175.354496693273</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4118.619766086411</v>
+        <v>4058.743816109261</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4059.767706027152</v>
+        <v>3947.870170747103</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3938.321274756924</v>
+        <v>3782.181457495512</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,15 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>4035.281472329891</v>
+        <v>3978.617456991792</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B86">
+        <v>3939.246889768326</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.734498303606</v>
+        <v>3669.987323129491</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.237769318303</v>
+        <v>3567.581274798182</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.059287232209</v>
+        <v>3513.458299242508</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.597722479602</v>
+        <v>3486.023848247849</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.150282184822</v>
+        <v>3494.586788918362</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3506.961963710389</v>
+        <v>3507.403592148722</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.464313648664</v>
+        <v>3521.902605517836</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3533.93750805068</v>
+        <v>3534.368768021527</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.462396995295</v>
+        <v>3549.784512223292</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.314269870662</v>
+        <v>3452.23450804815</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.954662642295</v>
+        <v>3449.884519132962</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.059927769912</v>
+        <v>3449.995179977543</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3531.059790417996</v>
+        <v>3530.714319081635</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.454604992303</v>
+        <v>3625.788627476041</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.658924672649</v>
+        <v>3775.6434575891</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.29313068979</v>
+        <v>3847.380705647117</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.284719414598</v>
+        <v>3894.4197877394</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.206523317541</v>
+        <v>3880.451508175563</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.71591852796</v>
+        <v>3885.393368363396</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.225449694854</v>
+        <v>3993.116597236875</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.860615985612</v>
+        <v>4066.545614256584</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.569678146007</v>
+        <v>4106.181523804959</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.245494025145</v>
+        <v>4206.211162522939</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.898195653069</v>
+        <v>4198.748551006029</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.199169465788</v>
+        <v>4221.775281321556</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.976294618451</v>
+        <v>4242.543732711086</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.74616413737</v>
+        <v>4306.134603910079</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.370947073035</v>
+        <v>4397.592590165773</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4434.087519421469</v>
+        <v>4433.235028743362</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.344023350177</v>
+        <v>4533.197162475528</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4668.661086959784</v>
+        <v>4667.270380669232</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4748.429895813269</v>
+        <v>4746.601136457874</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.29975569507</v>
+        <v>4887.246383617993</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4928.934341506471</v>
+        <v>4927.775930861706</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5033.692835450824</v>
+        <v>5032.171199889062</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.845094158414</v>
+        <v>5203.960612916026</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.533156670208</v>
+        <v>5250.334294632508</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.810046216997</v>
+        <v>5297.654059339249</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5377.781136698324</v>
+        <v>5379.435921757116</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5457.117423513592</v>
+        <v>5459.270945329361</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5588.425179606968</v>
+        <v>5590.794158760154</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5531.894753403658</v>
+        <v>5534.968268289045</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5361.048663074727</v>
+        <v>5364.910017031676</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5243.429778465638</v>
+        <v>5247.097696075316</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5111.089486531355</v>
+        <v>5115.081396191929</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4995.292765609234</v>
+        <v>4998.933801822448</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4891.878121299497</v>
+        <v>4895.397270342872</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4845.752346928734</v>
+        <v>4849.734809562974</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4713.219132614947</v>
+        <v>4716.410940252788</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4586.846732875287</v>
+        <v>4589.049910672455</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4486.976405831083</v>
+        <v>4488.399937361868</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4482.289388985795</v>
+        <v>4483.743217647549</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4404.378470090369</v>
+        <v>4406.214850706285</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4249.805088222853</v>
+        <v>4252.308493610066</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4165.061214434967</v>
+        <v>4156.309649603021</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4103.601679109728</v>
+        <v>4102.085242443594</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4078.088748912716</v>
+        <v>4082.107188226873</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4095.644575417714</v>
+        <v>4120.652381090493</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4150.569858559531</v>
+        <v>4193.390651412617</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4229.968484682555</v>
+        <v>4286.010547612204</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4270.070752102073</v>
+        <v>4329.559054676746</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4296.418709476651</v>
+        <v>4337.809741989042</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4304.978703083914</v>
+        <v>4333.818237265237</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4325.322113731112</v>
+        <v>4340.085297843896</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4350.677368011213</v>
+        <v>4351.44860263685</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4371.617337019001</v>
+        <v>4372.214968818016</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4398.037458644558</v>
+        <v>4417.003010843931</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4453.839117886395</v>
+        <v>4458.08704157076</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4472.504172923578</v>
+        <v>4483.321853549034</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4515.517114978314</v>
+        <v>4508.923101027744</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4538.677310151307</v>
+        <v>4522.593737983576</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4515.44220897185</v>
+        <v>4483.510856018</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4431.71678709173</v>
+        <v>4416.90984363718</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4293.155493237056</v>
+        <v>4302.217717891206</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4175.354496693273</v>
+        <v>4202.265447702825</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4058.743816109261</v>
+        <v>4105.187661322581</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>3947.870170747103</v>
+        <v>4044.463029777422</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3782.181457495512</v>
+        <v>3923.503620585447</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>3978.617456991792</v>
+        <v>3982.458540808041</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46402</v>
       </c>
       <c r="B86">
-        <v>3939.246889768326</v>
+        <v>3782.00229080804</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.987323129491</v>
+        <v>3669.759516212188</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.581274798182</v>
+        <v>3567.271752321746</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.458299242508</v>
+        <v>3513.09875292436</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3486.023848247849</v>
+        <v>3485.639858325485</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.586788918362</v>
+        <v>3494.193444973408</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3507.403592148722</v>
+        <v>3507.005633422164</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.902605517836</v>
+        <v>3521.507653673577</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3534.368768021527</v>
+        <v>3533.980152738533</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.784512223292</v>
+        <v>3549.494218171455</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.23450804815</v>
+        <v>3452.306367217655</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.884519132962</v>
+        <v>3449.947711625227</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3449.995179977543</v>
+        <v>3450.053510523851</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3530.714319081635</v>
+        <v>3531.02557379547</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3625.788627476041</v>
+        <v>3626.388662495406</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3775.6434575891</v>
+        <v>3776.558420746263</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3847.380705647117</v>
+        <v>3848.202843943176</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3894.4197877394</v>
+        <v>3895.199214931858</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3880.451508175563</v>
+        <v>3881.13192539516</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.393368363396</v>
+        <v>3885.684096357723</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.116597236875</v>
+        <v>3993.214737880019</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.545614256584</v>
+        <v>4066.829485634565</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.181523804959</v>
+        <v>4106.531313871601</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.211162522939</v>
+        <v>4206.242053041333</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.748551006029</v>
+        <v>4198.883314603416</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4221.775281321556</v>
+        <v>4222.157104648519</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.543732711086</v>
+        <v>4242.933398389587</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.134603910079</v>
+        <v>4306.685550901366</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4397.592590165773</v>
+        <v>4398.293846770775</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4433.235028743362</v>
+        <v>4434.00312911438</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4533.197162475528</v>
+        <v>4534.230554815815</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4667.270380669232</v>
+        <v>4668.523476041406</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4746.601136457874</v>
+        <v>4748.249252051495</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4887.246383617993</v>
+        <v>4888.195549109965</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4927.775930861706</v>
+        <v>4928.819748413664</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5032.171199889062</v>
+        <v>5033.542375234598</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5203.960612916026</v>
+        <v>5204.757799822599</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.334294632508</v>
+        <v>5250.513943720374</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5297.654059339249</v>
+        <v>5296.894143428553</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5379.435921757116</v>
+        <v>5377.945293954948</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5459.270945329361</v>
+        <v>5457.330993201618</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5590.794158760154</v>
+        <v>5588.66003062446</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5534.968268289045</v>
+        <v>5532.199057001408</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5364.910017031676</v>
+        <v>5361.430758215765</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5247.097696075316</v>
+        <v>5243.792568876052</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5115.081396191929</v>
+        <v>5111.484061381364</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4998.933801822448</v>
+        <v>4995.652470927178</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4895.397270342872</v>
+        <v>4892.225553943759</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4849.734809562974</v>
+        <v>4846.145505611866</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4716.410940252788</v>
+        <v>4713.534296446533</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4589.049910672455</v>
+        <v>4587.064455687395</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4488.399937361868</v>
+        <v>4487.117400537049</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4483.743217647549</v>
+        <v>4482.433370164519</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4406.214850706285</v>
+        <v>4404.560168483758</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4252.308493610066</v>
+        <v>4250.052396767365</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4156.309649603021</v>
+        <v>4165.275653534698</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4102.085242443594</v>
+        <v>4103.744681823338</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4082.107188226873</v>
+        <v>4078.117146296137</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4120.652381090493</v>
+        <v>4095.524814313759</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4193.390651412617</v>
+        <v>4150.250077472794</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4286.010547612204</v>
+        <v>4229.489444452457</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4329.559054676746</v>
+        <v>4269.544524867079</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4337.809741989042</v>
+        <v>4295.914768699317</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4333.818237265237</v>
+        <v>4304.473477213764</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4340.085297843896</v>
+        <v>4324.913355005005</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4351.44860263685</v>
+        <v>4350.441818244826</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4372.214968818016</v>
+        <v>4371.598053203613</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4417.003010843931</v>
+        <v>4391.690319973517</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4458.08704157076</v>
+        <v>4444.905468803245</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4483.321853549034</v>
+        <v>4463.397552488337</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4508.923101027744</v>
+        <v>4503.927548665113</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4522.593737983576</v>
+        <v>4523.870657239995</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4483.510856018</v>
+        <v>4501.582871531996</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4416.90984363718</v>
+        <v>4418.102258137144</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4302.217717891206</v>
+        <v>4281.192701738457</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4202.265447702825</v>
+        <v>4164.689355050248</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4105.187661322581</v>
+        <v>4049.451849321477</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>4044.463029777422</v>
+        <v>3941.50042174866</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3923.503620585447</v>
+        <v>3786.146617490548</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>3982.458540808041</v>
+        <v>3951.627485267757</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46402</v>
       </c>
       <c r="B86">
-        <v>3782.00229080804</v>
+        <v>3861.587455592965</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -399,114 +399,682 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3">
-        <v>46304</v>
+        <v>45814</v>
       </c>
       <c r="B2">
-        <v>4195.629999999999</v>
+        <v>3358.57</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3">
-        <v>46311</v>
+        <v>45821</v>
       </c>
       <c r="B3">
-        <v>4189.768588669531</v>
+        <v>3402.4778453743</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3">
-        <v>46318</v>
+        <v>45828</v>
       </c>
       <c r="B4">
-        <v>4181.420268944958</v>
+        <v>3417.94651939164</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3">
-        <v>46325</v>
+        <v>45835</v>
       </c>
       <c r="B5">
-        <v>4165.377148032574</v>
+        <v>3363.36102355087</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3">
-        <v>46332</v>
+        <v>45842</v>
       </c>
       <c r="B6">
-        <v>4177.32434515046</v>
+        <v>3373.03649920341</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3">
-        <v>46339</v>
+        <v>45849</v>
       </c>
       <c r="B7">
-        <v>4193.197933431535</v>
+        <v>3669.784095244165</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3">
-        <v>46346</v>
+        <v>45856</v>
       </c>
       <c r="B8">
-        <v>4207.083220511379</v>
+        <v>3567.305140906919</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3">
-        <v>46353</v>
+        <v>45863</v>
       </c>
       <c r="B9">
-        <v>4215.092452283078</v>
+        <v>3513.137530132589</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3">
-        <v>46360</v>
+        <v>45870</v>
       </c>
       <c r="B10">
-        <v>4211.971178172243</v>
+        <v>3485.681261596198</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3">
-        <v>46367</v>
+        <v>45877</v>
       </c>
       <c r="B11">
-        <v>4237.226828013049</v>
+        <v>3494.235857233998</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3">
-        <v>46374</v>
+        <v>45884</v>
       </c>
       <c r="B12">
-        <v>4118.831797473496</v>
+        <v>3507.048543689254</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3">
-        <v>46381</v>
+        <v>45891</v>
       </c>
       <c r="B13">
-        <v>4109.269259246614</v>
+        <v>3521.550239934912</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3">
-        <v>46388</v>
+        <v>45898</v>
       </c>
       <c r="B14">
-        <v>4101.588546849834</v>
+        <v>3534.022055754949</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3">
+        <v>45905</v>
+      </c>
+      <c r="B15">
+        <v>3549.525492521406</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3">
+        <v>45912</v>
+      </c>
+      <c r="B16">
+        <v>3452.298605322072</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3">
+        <v>45919</v>
+      </c>
+      <c r="B17">
+        <v>3449.940884699431</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3">
+        <v>45926</v>
+      </c>
+      <c r="B18">
+        <v>3450.047208038422</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="3">
+        <v>45933</v>
+      </c>
+      <c r="B19">
+        <v>3530.991964045421</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="3">
+        <v>45940</v>
+      </c>
+      <c r="B20">
+        <v>3626.323885686304</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3">
+        <v>45947</v>
+      </c>
+      <c r="B21">
+        <v>3776.459684126276</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="3">
+        <v>45954</v>
+      </c>
+      <c r="B22">
+        <v>3848.114140830751</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="3">
+        <v>45961</v>
+      </c>
+      <c r="B23">
+        <v>3895.115192498743</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="3">
+        <v>45968</v>
+      </c>
+      <c r="B24">
+        <v>3881.0586117947</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="3">
+        <v>45975</v>
+      </c>
+      <c r="B25">
+        <v>3885.652812036139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="3">
+        <v>45982</v>
+      </c>
+      <c r="B26">
+        <v>3993.204201250999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="3">
+        <v>45989</v>
+      </c>
+      <c r="B27">
+        <v>4066.798892798948</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="3">
+        <v>45996</v>
+      </c>
+      <c r="B28">
+        <v>4106.493612983875</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="3">
+        <v>46003</v>
+      </c>
+      <c r="B29">
+        <v>4206.238681780989</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="3">
+        <v>46010</v>
+      </c>
+      <c r="B30">
+        <v>4198.868710244219</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="3">
+        <v>46017</v>
+      </c>
+      <c r="B31">
+        <v>4222.115803291013</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="3">
+        <v>46024</v>
+      </c>
+      <c r="B32">
+        <v>4242.891274427368</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3">
+        <v>46031</v>
+      </c>
+      <c r="B33">
+        <v>4306.626021656817</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="3">
+        <v>46038</v>
+      </c>
+      <c r="B34">
+        <v>4398.218115781337</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B35">
+        <v>4433.920226229937</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B36">
+        <v>4534.119072949237</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3">
+        <v>46059</v>
+      </c>
+      <c r="B37">
+        <v>4668.388278041461</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3">
+        <v>46066</v>
+      </c>
+      <c r="B38">
+        <v>4748.071709007386</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3">
+        <v>46073</v>
+      </c>
+      <c r="B39">
+        <v>4888.093164365931</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B40">
+        <v>4928.707157765572</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B41">
+        <v>5033.394530449043</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3">
+        <v>46094</v>
+      </c>
+      <c r="B42">
+        <v>5204.671987920327</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="3">
+        <v>46101</v>
+      </c>
+      <c r="B43">
+        <v>5250.494968250243</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B44">
+        <v>5296.976641586059</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3">
+        <v>46115</v>
+      </c>
+      <c r="B45">
+        <v>5378.106483899388</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3">
+        <v>46122</v>
+      </c>
+      <c r="B46">
+        <v>5457.540715924953</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3">
+        <v>46129</v>
+      </c>
+      <c r="B47">
+        <v>5588.890669657181</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3">
+        <v>46136</v>
+      </c>
+      <c r="B48">
+        <v>5532.497986711407</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B49">
+        <v>5361.806151008663</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B50">
+        <v>5244.149030561372</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B51">
+        <v>5111.871808957761</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B52">
+        <v>4996.005992345924</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B53">
+        <v>4892.567063159153</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B54">
+        <v>4846.531964588268</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B55">
+        <v>4713.844076624035</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B56">
+        <v>4587.278421253874</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B57">
+        <v>4487.255894048839</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B58">
+        <v>4482.574800185045</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B59">
+        <v>4404.738683641927</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B60">
+        <v>4250.295455838254</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B61">
+        <v>4165.486509366344</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B62">
+        <v>4103.88541807502</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B63">
+        <v>4078.145356820896</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B64">
+        <v>4095.40751236493</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B65">
+        <v>4149.936217214075</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B66">
+        <v>4229.018939985472</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B67">
+        <v>4269.027215658212</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B68">
+        <v>4295.418930721802</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B69">
+        <v>4303.975822695995</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B70">
+        <v>4324.510093705934</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B71">
+        <v>4350.208380882902</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B72">
+        <v>4371.576944959656</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B73">
+        <v>4385.638063940172</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B74">
+        <v>4436.538365393134</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B75">
+        <v>4454.850546733288</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B76">
+        <v>4493.126342652583</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B77">
+        <v>4511.629442035457</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B78">
+        <v>4488.709450827589</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B79">
+        <v>4405.547567204871</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B80">
+        <v>4270.294823314441</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B81">
+        <v>4155.145558119986</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B82">
+        <v>4041.41713935912</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B83">
+        <v>3936.40294146458</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B84">
+        <v>3790.277455192461</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
         <v>46395</v>
       </c>
-      <c r="B15">
-        <v>4095.961647528358</v>
+      <c r="B85">
+        <v>3932.70266006803</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B86">
+        <v>3839.267516554958</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/XAUUSD_forecast.xlsx
+++ b/public/data/files/XAUUSD_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>3669.784095244165</v>
+        <v>3669.808246847323</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>3567.305140906919</v>
+        <v>3567.337950533718</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>3513.137530132589</v>
+        <v>3513.175636715236</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>3485.681261596198</v>
+        <v>3485.721951228454</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>3494.235857233998</v>
+        <v>3494.277538369915</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>3507.048543689254</v>
+        <v>3507.090714148168</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>3521.550239934912</v>
+        <v>3521.592091923671</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>3534.022055754949</v>
+        <v>3534.063236278292</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>3549.525492521406</v>
+        <v>3549.556234012565</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>3452.298605322072</v>
+        <v>3452.290980457687</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>3449.940884699431</v>
+        <v>3449.934178572648</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>3450.047208038422</v>
+        <v>3450.041017263881</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>3530.991964045421</v>
+        <v>3530.958945168903</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>3626.323885686304</v>
+        <v>3626.260243936545</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>3776.459684126276</v>
+        <v>3776.362668616905</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>3848.114140830751</v>
+        <v>3848.026980057883</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>3895.115192498743</v>
+        <v>3895.03261393417</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>3881.0586117947</v>
+        <v>3880.986549657144</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>3885.652812036139</v>
+        <v>3885.622052063209</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>3993.204201250999</v>
+        <v>3993.193835565561</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>4066.798892798948</v>
+        <v>4066.768823678052</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>4106.493612983875</v>
+        <v>4106.456558427659</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>4206.238681780989</v>
+        <v>4206.235378183464</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>4198.868710244219</v>
+        <v>4198.854374958719</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>4222.115803291013</v>
+        <v>4222.075244833315</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>4242.891274427368</v>
+        <v>4242.849902100982</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>4306.626021656817</v>
+        <v>4306.567547630688</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>4398.218115781337</v>
+        <v>4398.143718004683</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>4433.920226229937</v>
+        <v>4433.838771833032</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>4534.119072949237</v>
+        <v>4534.009526075795</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>4668.388278041461</v>
+        <v>4668.255430114377</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>4748.071709007386</v>
+        <v>4747.897187605152</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>4888.093164365931</v>
+        <v>4887.992554154376</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>4928.707157765572</v>
+        <v>4928.596517588503</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>5033.394530449043</v>
+        <v>5033.249233590421</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>5204.671987920327</v>
+        <v>5204.587621088867</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>5250.494968250243</v>
+        <v>5250.47622666413</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>5296.976641586059</v>
+        <v>5297.057585566718</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>5378.106483899388</v>
+        <v>5378.264786124102</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>5457.540715924953</v>
+        <v>5457.746694503279</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>5588.890669657181</v>
+        <v>5589.117208838441</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>5532.497986711407</v>
+        <v>5532.791683492936</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>5361.806151008663</v>
+        <v>5362.175016029995</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>5244.149030561372</v>
+        <v>5244.499327450665</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>5111.871808957761</v>
+        <v>5112.252904648323</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>4996.005992345924</v>
+        <v>4996.353487747851</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>4892.567063159153</v>
+        <v>4892.902798888086</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>4846.531964588268</v>
+        <v>4846.911893344487</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>4713.844076624035</v>
+        <v>4714.148609704247</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>4587.278421253874</v>
+        <v>4587.488725883737</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>4487.255894048839</v>
+        <v>4487.391952230174</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>4482.574800185045</v>
+        <v>4482.713746166071</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>4404.738683641927</v>
+        <v>4404.914098359096</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>4250.295455838254</v>
+        <v>4250.534373715605</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>4165.486509366344</v>
+        <v>4165.693870529993</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>4103.88541807502</v>
+        <v>4104.023940625687</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>4078.145356820896</v>
+        <v>4078.173377559436</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>4095.40751236493</v>
+        <v>4095.292596965668</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>4149.936217214075</v>
+        <v>4149.62811705273</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>4229.018939985472</v>
+        <v>4228.556748096829</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>4269.027215658212</v>
+        <v>4268.51860354826</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>4295.418930721802</v>
+        <v>4294.931007060491</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>4303.975822695995</v>
+        <v>4303.485578324281</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>4324.510093705934</v>
+        <v>4324.112230178504</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>4350.208380882902</v>
+        <v>4349.977051078514</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>4371.576944959656</v>
+        <v>4371.554110265526</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>4385.638063940172</v>
+        <v>4380.533599363192</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>4436.538365393134</v>
+        <v>4429.468533776163</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>4454.850546733288</v>
+        <v>4447.808649737352</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>4493.126342652583</v>
+        <v>4485.293486719724</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>4511.629442035457</v>
+        <v>4502.613110679731</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>4488.709450827589</v>
+        <v>4479.237637904536</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>4405.547567204871</v>
+        <v>4396.63887858799</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>4270.294823314441</v>
+        <v>4263.320580582343</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>4155.145558119986</v>
+        <v>4150.020032702643</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>4041.41713935912</v>
+        <v>4038.95263847368</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>3936.40294146458</v>
+        <v>3938.033553947728</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>3790.277455192461</v>
+        <v>3802.194633615296</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>3932.70266006803</v>
+        <v>3930.981026732133</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46402</v>
       </c>
       <c r="B86">
-        <v>3839.267516554958</v>
+        <v>3857.42176396357</v>
       </c>
     </row>
   </sheetData>
